--- a/research/traditional_assets/database/data/oman/oman_oil_gas_production_and_exploration.xlsx
+++ b/research/traditional_assets/database/data/oman/oman_oil_gas_production_and_exploration.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.119596716704932</v>
+        <v>0.1194555716298746</v>
       </c>
       <c r="C2">
-        <v>838.4359433868452</v>
+        <v>831.9149056215213</v>
       </c>
       <c r="D2">
-        <v>825.5359433868452</v>
+        <v>827.1179056215212</v>
       </c>
       <c r="E2">
-        <v>-256.2</v>
+        <v>-248.097</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>8.103</v>
       </c>
       <c r="G2">
         <v>12.9</v>
@@ -1439,28 +1439,28 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.4075809</v>
       </c>
       <c r="N2">
-        <v>78.11428571428573</v>
+        <v>77.70670481428573</v>
       </c>
       <c r="O2">
-        <v>11.71714285714286</v>
+        <v>11.65600572214286</v>
       </c>
       <c r="P2">
-        <v>66.39714285714287</v>
+        <v>66.05069909214286</v>
       </c>
       <c r="Q2">
-        <v>118.9971428571429</v>
+        <v>118.6506990921429</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.119596716704932</v>
+        <v>0.1202303248786612</v>
       </c>
       <c r="T2">
-        <v>0.9618186075065634</v>
+        <v>0.9700766460558621</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>191.653450184456</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1194555716298746</v>
+        <v>0.1193144265548172</v>
       </c>
       <c r="C3">
-        <v>831.9149056215213</v>
+        <v>825.3999424782492</v>
       </c>
       <c r="D3">
-        <v>827.1179056215212</v>
+        <v>828.7059424782492</v>
       </c>
       <c r="E3">
-        <v>-248.097</v>
+        <v>-239.994</v>
       </c>
       <c r="F3">
-        <v>8.103</v>
+        <v>16.206</v>
       </c>
       <c r="G3">
         <v>12.9</v>
@@ -1521,28 +1521,28 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M3">
-        <v>0.4075809</v>
+        <v>0.8151617999999999</v>
       </c>
       <c r="N3">
-        <v>77.70670481428573</v>
+        <v>77.29912391428573</v>
       </c>
       <c r="O3">
-        <v>11.65600572214286</v>
+        <v>11.59486858714286</v>
       </c>
       <c r="P3">
-        <v>66.05069909214286</v>
+        <v>65.70425532714287</v>
       </c>
       <c r="Q3">
-        <v>118.6506990921429</v>
+        <v>118.3042553271429</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1202303248786612</v>
+        <v>0.1208768638314461</v>
       </c>
       <c r="T3">
-        <v>0.9700766460558621</v>
+        <v>0.9785032160041264</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>191.653450184456</v>
+        <v>95.82672509222799</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1193144265548172</v>
+        <v>0.1191732814797598</v>
       </c>
       <c r="C4">
-        <v>825.3999424782492</v>
+        <v>818.8910890135089</v>
       </c>
       <c r="D4">
-        <v>828.7059424782492</v>
+        <v>830.3000890135089</v>
       </c>
       <c r="E4">
-        <v>-239.994</v>
+        <v>-231.891</v>
       </c>
       <c r="F4">
-        <v>16.206</v>
+        <v>24.309</v>
       </c>
       <c r="G4">
         <v>12.9</v>
@@ -1603,28 +1603,28 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M4">
-        <v>0.8151617999999999</v>
+        <v>1.2227427</v>
       </c>
       <c r="N4">
-        <v>77.29912391428573</v>
+        <v>76.89154301428573</v>
       </c>
       <c r="O4">
-        <v>11.59486858714286</v>
+        <v>11.53373145214286</v>
       </c>
       <c r="P4">
-        <v>65.70425532714287</v>
+        <v>65.35781156214287</v>
       </c>
       <c r="Q4">
-        <v>118.3042553271429</v>
+        <v>117.9578115621429</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1208768638314461</v>
+        <v>0.1215367334842884</v>
       </c>
       <c r="T4">
-        <v>0.9785032160041264</v>
+        <v>0.9871035296626638</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>95.82672509222799</v>
+        <v>63.88448339481867</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1191732814797598</v>
+        <v>0.1190321364047023</v>
       </c>
       <c r="C5">
-        <v>818.8910890135089</v>
+        <v>812.3883805540472</v>
       </c>
       <c r="D5">
-        <v>830.3000890135089</v>
+        <v>831.9003805540473</v>
       </c>
       <c r="E5">
-        <v>-231.891</v>
+        <v>-223.788</v>
       </c>
       <c r="F5">
-        <v>24.309</v>
+        <v>32.412</v>
       </c>
       <c r="G5">
         <v>12.9</v>
@@ -1685,28 +1685,28 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M5">
-        <v>1.2227427</v>
+        <v>1.6303236</v>
       </c>
       <c r="N5">
-        <v>76.89154301428573</v>
+        <v>76.48396211428573</v>
       </c>
       <c r="O5">
-        <v>11.53373145214286</v>
+        <v>11.47259431714286</v>
       </c>
       <c r="P5">
-        <v>65.35781156214287</v>
+        <v>65.01136779714287</v>
       </c>
       <c r="Q5">
-        <v>117.9578115621429</v>
+        <v>117.6113677971429</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1215367334842884</v>
+        <v>0.1222103504215649</v>
       </c>
       <c r="T5">
-        <v>0.9871035296626638</v>
+        <v>0.9958830165224208</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>63.88448339481867</v>
+        <v>47.91336254611399</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1190321364047023</v>
+        <v>0.118890991329645</v>
       </c>
       <c r="C6">
-        <v>812.3883805540472</v>
+        <v>805.891852699486</v>
       </c>
       <c r="D6">
-        <v>831.9003805540473</v>
+        <v>833.506852699486</v>
       </c>
       <c r="E6">
-        <v>-223.788</v>
+        <v>-215.685</v>
       </c>
       <c r="F6">
-        <v>32.412</v>
+        <v>40.515</v>
       </c>
       <c r="G6">
         <v>12.9</v>
@@ -1767,28 +1767,28 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M6">
-        <v>1.6303236</v>
+        <v>2.0379045</v>
       </c>
       <c r="N6">
-        <v>76.48396211428573</v>
+        <v>76.07638121428573</v>
       </c>
       <c r="O6">
-        <v>11.47259431714286</v>
+        <v>11.41145718214286</v>
       </c>
       <c r="P6">
-        <v>65.01136779714287</v>
+        <v>64.66492403214288</v>
       </c>
       <c r="Q6">
-        <v>117.6113677971429</v>
+        <v>117.2649240321429</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1222103504215649</v>
+        <v>0.1228981487680473</v>
       </c>
       <c r="T6">
-        <v>0.9958830165224208</v>
+        <v>1.004847334684489</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>47.91336254611399</v>
+        <v>38.3306900368912</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.118890991329645</v>
+        <v>0.1187498462545876</v>
       </c>
       <c r="C7">
-        <v>805.891852699486</v>
+        <v>799.4015413249635</v>
       </c>
       <c r="D7">
-        <v>833.506852699486</v>
+        <v>835.1195413249636</v>
       </c>
       <c r="E7">
-        <v>-215.685</v>
+        <v>-207.582</v>
       </c>
       <c r="F7">
-        <v>40.515</v>
+        <v>48.618</v>
       </c>
       <c r="G7">
         <v>12.9</v>
@@ -1849,28 +1849,28 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M7">
-        <v>2.0379045</v>
+        <v>2.4454854</v>
       </c>
       <c r="N7">
-        <v>76.07638121428573</v>
+        <v>75.66880031428573</v>
       </c>
       <c r="O7">
-        <v>11.41145718214286</v>
+        <v>11.35032004714286</v>
       </c>
       <c r="P7">
-        <v>64.66492403214288</v>
+        <v>64.31848026714287</v>
       </c>
       <c r="Q7">
-        <v>117.2649240321429</v>
+        <v>116.9184802671429</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1228981487680473</v>
+        <v>0.1236005811219017</v>
       </c>
       <c r="T7">
-        <v>1.004847334684489</v>
+        <v>1.014002383020217</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>38.3306900368912</v>
+        <v>31.94224169740933</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1187498462545876</v>
+        <v>0.1186087011795302</v>
       </c>
       <c r="C8">
-        <v>799.4015413249635</v>
+        <v>792.9174825838048</v>
       </c>
       <c r="D8">
-        <v>835.1195413249636</v>
+        <v>836.7384825838049</v>
       </c>
       <c r="E8">
-        <v>-207.582</v>
+        <v>-199.479</v>
       </c>
       <c r="F8">
-        <v>48.61799999999999</v>
+        <v>56.72099999999999</v>
       </c>
       <c r="G8">
         <v>12.9</v>
@@ -1931,28 +1931,28 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M8">
-        <v>2.445485399999999</v>
+        <v>2.853066299999999</v>
       </c>
       <c r="N8">
-        <v>75.66880031428573</v>
+        <v>75.26121941428573</v>
       </c>
       <c r="O8">
-        <v>11.35032004714286</v>
+        <v>11.28918291214286</v>
       </c>
       <c r="P8">
-        <v>64.31848026714287</v>
+        <v>63.97203650214287</v>
       </c>
       <c r="Q8">
-        <v>116.9184802671429</v>
+        <v>116.5720365021429</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1236005811219017</v>
+        <v>0.1243181195478819</v>
       </c>
       <c r="T8">
-        <v>1.014002383020217</v>
+        <v>1.023354314115854</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>31.94224169740934</v>
+        <v>27.37906431206515</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1186087011795302</v>
+        <v>0.1184675561044728</v>
       </c>
       <c r="C9">
-        <v>792.9174825838051</v>
+        <v>786.4397129102236</v>
       </c>
       <c r="D9">
-        <v>836.7384825838051</v>
+        <v>838.3637129102236</v>
       </c>
       <c r="E9">
-        <v>-199.479</v>
+        <v>-191.376</v>
       </c>
       <c r="F9">
-        <v>56.721</v>
+        <v>64.824</v>
       </c>
       <c r="G9">
         <v>12.9</v>
@@ -2013,28 +2013,28 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M9">
-        <v>2.8530663</v>
+        <v>3.2606472</v>
       </c>
       <c r="N9">
-        <v>75.26121941428573</v>
+        <v>74.85363851428573</v>
       </c>
       <c r="O9">
-        <v>11.28918291214286</v>
+        <v>11.22804577714286</v>
       </c>
       <c r="P9">
-        <v>63.97203650214287</v>
+        <v>63.62559273714287</v>
       </c>
       <c r="Q9">
-        <v>116.5720365021429</v>
+        <v>116.2255927371429</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1243181195478819</v>
+        <v>0.1250512566352965</v>
       </c>
       <c r="T9">
-        <v>1.023354314115854</v>
+        <v>1.032909548061396</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>27.37906431206514</v>
+        <v>23.956681273057</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1184675561044728</v>
+        <v>0.1183264110294154</v>
       </c>
       <c r="C10">
-        <v>786.4397129102236</v>
+        <v>779.9682690220533</v>
       </c>
       <c r="D10">
-        <v>838.3637129102236</v>
+        <v>839.9952690220533</v>
       </c>
       <c r="E10">
-        <v>-191.376</v>
+        <v>-183.273</v>
       </c>
       <c r="F10">
-        <v>64.824</v>
+        <v>72.92699999999999</v>
       </c>
       <c r="G10">
         <v>12.9</v>
@@ -2095,28 +2095,28 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M10">
-        <v>3.2606472</v>
+        <v>3.668228099999999</v>
       </c>
       <c r="N10">
-        <v>74.85363851428573</v>
+        <v>74.44605761428573</v>
       </c>
       <c r="O10">
-        <v>11.22804577714286</v>
+        <v>11.16690864214286</v>
       </c>
       <c r="P10">
-        <v>63.62559273714287</v>
+        <v>63.27914897214288</v>
       </c>
       <c r="Q10">
-        <v>116.2255927371429</v>
+        <v>115.8791489721429</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1250512566352965</v>
+        <v>0.1258005066257312</v>
       </c>
       <c r="T10">
-        <v>1.032909548061396</v>
+        <v>1.042674787148599</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>23.956681273057</v>
+        <v>21.29482779827289</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1183264110294154</v>
+        <v>0.118185265954358</v>
       </c>
       <c r="C11">
-        <v>779.9682690220533</v>
+        <v>773.5031879235149</v>
       </c>
       <c r="D11">
-        <v>839.9952690220533</v>
+        <v>841.6331879235149</v>
       </c>
       <c r="E11">
-        <v>-183.273</v>
+        <v>-175.17</v>
       </c>
       <c r="F11">
-        <v>72.92699999999999</v>
+        <v>81.02999999999999</v>
       </c>
       <c r="G11">
         <v>12.9</v>
@@ -2177,28 +2177,28 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M11">
-        <v>3.668228099999999</v>
+        <v>4.075809</v>
       </c>
       <c r="N11">
-        <v>74.44605761428573</v>
+        <v>74.03847671428574</v>
       </c>
       <c r="O11">
-        <v>11.16690864214286</v>
+        <v>11.10577150714286</v>
       </c>
       <c r="P11">
-        <v>63.27914897214288</v>
+        <v>62.93270520714287</v>
       </c>
       <c r="Q11">
-        <v>115.8791489721429</v>
+        <v>115.5327052071429</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1258005066257312</v>
+        <v>0.1265664066159533</v>
       </c>
       <c r="T11">
-        <v>1.042674787148599</v>
+        <v>1.05265703154885</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>21.29482779827289</v>
+        <v>19.1653450184456</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.118185265954358</v>
+        <v>0.1180441208793006</v>
       </c>
       <c r="C12">
-        <v>773.5031879235149</v>
+        <v>767.0445069080138</v>
       </c>
       <c r="D12">
-        <v>841.6331879235149</v>
+        <v>843.2775069080138</v>
       </c>
       <c r="E12">
-        <v>-175.17</v>
+        <v>-167.067</v>
       </c>
       <c r="F12">
-        <v>81.03</v>
+        <v>89.133</v>
       </c>
       <c r="G12">
         <v>12.9</v>
@@ -2259,28 +2259,28 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M12">
-        <v>4.075809</v>
+        <v>4.4833899</v>
       </c>
       <c r="N12">
-        <v>74.03847671428574</v>
+        <v>73.63089581428572</v>
       </c>
       <c r="O12">
-        <v>11.10577150714286</v>
+        <v>11.04463437214286</v>
       </c>
       <c r="P12">
-        <v>62.93270520714287</v>
+        <v>62.58626144214286</v>
       </c>
       <c r="Q12">
-        <v>115.5327052071429</v>
+        <v>115.1862614421429</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1265664066159533</v>
+        <v>0.1273495178419108</v>
       </c>
       <c r="T12">
-        <v>1.05265703154885</v>
+        <v>1.062863596047983</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>19.1653450184456</v>
+        <v>17.42304092585963</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1180441208793006</v>
+        <v>0.1179029758042432</v>
       </c>
       <c r="C13">
-        <v>767.0445069080138</v>
+        <v>760.5922635609692</v>
       </c>
       <c r="D13">
-        <v>843.2775069080138</v>
+        <v>844.9282635609692</v>
       </c>
       <c r="E13">
-        <v>-167.067</v>
+        <v>-158.964</v>
       </c>
       <c r="F13">
-        <v>89.133</v>
+        <v>97.23599999999999</v>
       </c>
       <c r="G13">
         <v>12.9</v>
@@ -2341,28 +2341,28 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M13">
-        <v>4.4833899</v>
+        <v>4.890970799999999</v>
       </c>
       <c r="N13">
-        <v>73.63089581428572</v>
+        <v>73.22331491428572</v>
       </c>
       <c r="O13">
-        <v>11.04463437214286</v>
+        <v>10.98349723714286</v>
       </c>
       <c r="P13">
-        <v>62.58626144214286</v>
+        <v>62.23981767714287</v>
       </c>
       <c r="Q13">
-        <v>115.1862614421429</v>
+        <v>114.8398176771429</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1273495178419108</v>
+        <v>0.1281504270502763</v>
       </c>
       <c r="T13">
-        <v>1.062863596047983</v>
+        <v>1.073302127922097</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>17.42304092585963</v>
+        <v>15.97112084870467</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1179029758042432</v>
+        <v>0.1177618307291858</v>
       </c>
       <c r="C14">
-        <v>760.5922635609692</v>
+        <v>754.1464957626797</v>
       </c>
       <c r="D14">
-        <v>844.9282635609692</v>
+        <v>846.5854957626797</v>
       </c>
       <c r="E14">
-        <v>-158.964</v>
+        <v>-150.861</v>
       </c>
       <c r="F14">
-        <v>97.23599999999999</v>
+        <v>105.339</v>
       </c>
       <c r="G14">
         <v>12.9</v>
@@ -2423,28 +2423,28 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M14">
-        <v>4.890970799999999</v>
+        <v>5.2985517</v>
       </c>
       <c r="N14">
-        <v>73.22331491428572</v>
+        <v>72.81573401428572</v>
       </c>
       <c r="O14">
-        <v>10.98349723714286</v>
+        <v>10.92236010214286</v>
       </c>
       <c r="P14">
-        <v>62.23981767714287</v>
+        <v>61.89337391214286</v>
       </c>
       <c r="Q14">
-        <v>114.8398176771429</v>
+        <v>114.4933739121429</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1281504270502763</v>
+        <v>0.1289697479645814</v>
       </c>
       <c r="T14">
-        <v>1.073302127922097</v>
+        <v>1.08398062604619</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>15.97112084870467</v>
+        <v>14.742573091112</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1177618307291858</v>
+        <v>0.1176206856541284</v>
       </c>
       <c r="C15">
-        <v>754.1464957626797</v>
+        <v>747.7072416912184</v>
       </c>
       <c r="D15">
-        <v>846.5854957626797</v>
+        <v>848.2492416912185</v>
       </c>
       <c r="E15">
-        <v>-150.861</v>
+        <v>-142.758</v>
       </c>
       <c r="F15">
-        <v>105.339</v>
+        <v>113.442</v>
       </c>
       <c r="G15">
         <v>12.9</v>
@@ -2505,28 +2505,28 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M15">
-        <v>5.2985517</v>
+        <v>5.7061326</v>
       </c>
       <c r="N15">
-        <v>72.81573401428572</v>
+        <v>72.40815311428572</v>
       </c>
       <c r="O15">
-        <v>10.92236010214286</v>
+        <v>10.86122296714286</v>
       </c>
       <c r="P15">
-        <v>61.89337391214286</v>
+        <v>61.54693014714287</v>
       </c>
       <c r="Q15">
-        <v>114.4933739121429</v>
+        <v>114.1469301471429</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1289697479645814</v>
+        <v>0.1298081228536377</v>
       </c>
       <c r="T15">
-        <v>1.08398062604619</v>
+        <v>1.09490746133596</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>14.742573091112</v>
+        <v>13.68953215603257</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1176206856541284</v>
+        <v>0.117670790579071</v>
       </c>
       <c r="C16">
-        <v>747.7072416912184</v>
+        <v>739.0128823330549</v>
       </c>
       <c r="D16">
-        <v>848.2492416912185</v>
+        <v>847.6578823330549</v>
       </c>
       <c r="E16">
-        <v>-142.758</v>
+        <v>-134.655</v>
       </c>
       <c r="F16">
-        <v>113.442</v>
+        <v>121.545</v>
       </c>
       <c r="G16">
         <v>12.9</v>
@@ -2587,45 +2587,45 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M16">
-        <v>5.7061326</v>
+        <v>6.296031000000001</v>
       </c>
       <c r="N16">
-        <v>72.40815311428572</v>
+        <v>71.81825471428573</v>
       </c>
       <c r="O16">
-        <v>10.86122296714286</v>
+        <v>10.77273820714286</v>
       </c>
       <c r="P16">
-        <v>61.54693014714287</v>
+        <v>61.04551650714287</v>
       </c>
       <c r="Q16">
-        <v>114.1469301471429</v>
+        <v>113.6455165071429</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1298081228536377</v>
+        <v>0.1306662242106717</v>
       </c>
       <c r="T16">
-        <v>1.09490746133596</v>
+        <v>1.106091398632548</v>
       </c>
       <c r="U16">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V16">
         <v>0.15</v>
       </c>
       <c r="W16">
-        <v>0.04275499999999999</v>
+        <v>0.04403</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y16">
-        <v>13.68953215603257</v>
+        <v>12.40690932339528</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.117670790579071</v>
+        <v>0.1175423955040136</v>
       </c>
       <c r="C17">
-        <v>739.0128823330549</v>
+        <v>732.4269085859493</v>
       </c>
       <c r="D17">
-        <v>847.6578823330549</v>
+        <v>849.1749085859493</v>
       </c>
       <c r="E17">
-        <v>-134.655</v>
+        <v>-126.552</v>
       </c>
       <c r="F17">
-        <v>121.545</v>
+        <v>129.648</v>
       </c>
       <c r="G17">
         <v>12.9</v>
@@ -2669,28 +2669,28 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M17">
-        <v>6.296030999999999</v>
+        <v>6.7157664</v>
       </c>
       <c r="N17">
-        <v>71.81825471428573</v>
+        <v>71.39851931428572</v>
       </c>
       <c r="O17">
-        <v>10.77273820714286</v>
+        <v>10.70977789714286</v>
       </c>
       <c r="P17">
-        <v>61.04551650714287</v>
+        <v>60.68874141714286</v>
       </c>
       <c r="Q17">
-        <v>113.6455165071429</v>
+        <v>113.2887414171429</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1306662242106717</v>
+        <v>0.1315447565523971</v>
       </c>
       <c r="T17">
-        <v>1.106091398632548</v>
+        <v>1.117541620150483</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>12.40690932339528</v>
+        <v>11.63147749068308</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1175423955040136</v>
+        <v>0.1174140004289562</v>
       </c>
       <c r="C18">
-        <v>732.4269085859493</v>
+        <v>725.8463745209859</v>
       </c>
       <c r="D18">
-        <v>849.1749085859493</v>
+        <v>850.6973745209859</v>
       </c>
       <c r="E18">
-        <v>-126.552</v>
+        <v>-118.449</v>
       </c>
       <c r="F18">
-        <v>129.648</v>
+        <v>137.751</v>
       </c>
       <c r="G18">
         <v>12.9</v>
@@ -2751,28 +2751,28 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M18">
-        <v>6.7157664</v>
+        <v>7.1355018</v>
       </c>
       <c r="N18">
-        <v>71.39851931428572</v>
+        <v>70.97878391428573</v>
       </c>
       <c r="O18">
-        <v>10.70977789714286</v>
+        <v>10.64681758714286</v>
       </c>
       <c r="P18">
-        <v>60.68874141714286</v>
+        <v>60.33196632714287</v>
       </c>
       <c r="Q18">
-        <v>113.2887414171429</v>
+        <v>112.9319663271429</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1315447565523971</v>
+        <v>0.13244445834814</v>
       </c>
       <c r="T18">
-        <v>1.117541620150483</v>
+        <v>1.129267750620658</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>11.63147749068308</v>
+        <v>10.9472729324076</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1174140004289562</v>
+        <v>0.1172856053538988</v>
       </c>
       <c r="C19">
-        <v>725.8463745209859</v>
+        <v>719.2713094487523</v>
       </c>
       <c r="D19">
-        <v>850.6973745209859</v>
+        <v>852.2253094487523</v>
       </c>
       <c r="E19">
-        <v>-118.449</v>
+        <v>-110.346</v>
       </c>
       <c r="F19">
-        <v>137.751</v>
+        <v>145.854</v>
       </c>
       <c r="G19">
         <v>12.9</v>
@@ -2833,28 +2833,28 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M19">
-        <v>7.1355018</v>
+        <v>7.555237200000001</v>
       </c>
       <c r="N19">
-        <v>70.97878391428573</v>
+        <v>70.55904851428573</v>
       </c>
       <c r="O19">
-        <v>10.64681758714286</v>
+        <v>10.58385727714286</v>
       </c>
       <c r="P19">
-        <v>60.33196632714287</v>
+        <v>59.97519123714287</v>
       </c>
       <c r="Q19">
-        <v>112.9319663271429</v>
+        <v>112.5751912371429</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.13244445834814</v>
+        <v>0.1333661040901205</v>
       </c>
       <c r="T19">
-        <v>1.129267750620658</v>
+        <v>1.141279884273032</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>10.9472729324076</v>
+        <v>10.3390911028294</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1172856053538988</v>
+        <v>0.1174317602788414</v>
       </c>
       <c r="C20">
-        <v>719.2713094487522</v>
+        <v>709.4294588934706</v>
       </c>
       <c r="D20">
-        <v>852.2253094487521</v>
+        <v>850.4864588934706</v>
       </c>
       <c r="E20">
-        <v>-110.346</v>
+        <v>-102.243</v>
       </c>
       <c r="F20">
-        <v>145.854</v>
+        <v>153.957</v>
       </c>
       <c r="G20">
         <v>12.9</v>
@@ -2915,45 +2915,45 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M20">
-        <v>7.555237199999999</v>
+        <v>8.2366995</v>
       </c>
       <c r="N20">
-        <v>70.55904851428573</v>
+        <v>69.87758621428573</v>
       </c>
       <c r="O20">
-        <v>10.58385727714286</v>
+        <v>10.48163793214286</v>
       </c>
       <c r="P20">
-        <v>59.97519123714287</v>
+        <v>59.39594828214287</v>
       </c>
       <c r="Q20">
-        <v>112.5751912371429</v>
+        <v>111.9959482821429</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1333661040901205</v>
+        <v>0.1343105065170881</v>
       </c>
       <c r="T20">
-        <v>1.141279884273032</v>
+        <v>1.153588613818057</v>
       </c>
       <c r="U20">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V20">
         <v>0.15</v>
       </c>
       <c r="W20">
-        <v>0.04403</v>
+        <v>0.04547499999999999</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y20">
-        <v>10.33909110282941</v>
+        <v>9.483687697273128</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1174317602788414</v>
+        <v>0.117317815203784</v>
       </c>
       <c r="C21">
-        <v>709.4294588934706</v>
+        <v>702.6814883098166</v>
       </c>
       <c r="D21">
-        <v>850.4864588934706</v>
+        <v>851.8414883098166</v>
       </c>
       <c r="E21">
-        <v>-102.243</v>
+        <v>-94.13999999999999</v>
       </c>
       <c r="F21">
-        <v>153.957</v>
+        <v>162.06</v>
       </c>
       <c r="G21">
         <v>12.9</v>
@@ -2997,28 +2997,28 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M21">
-        <v>8.2366995</v>
+        <v>8.670209999999999</v>
       </c>
       <c r="N21">
-        <v>69.87758621428573</v>
+        <v>69.44407571428573</v>
       </c>
       <c r="O21">
-        <v>10.48163793214286</v>
+        <v>10.41661135714286</v>
       </c>
       <c r="P21">
-        <v>59.39594828214287</v>
+        <v>59.02746435714288</v>
       </c>
       <c r="Q21">
-        <v>111.9959482821429</v>
+        <v>111.6274643571429</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1343105065170881</v>
+        <v>0.13527851900473</v>
       </c>
       <c r="T21">
-        <v>1.153588613818057</v>
+        <v>1.166205061601708</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>9.483687697273128</v>
+        <v>9.009503312409473</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.117317815203784</v>
+        <v>0.1172038701287266</v>
       </c>
       <c r="C22">
-        <v>702.6814883098166</v>
+        <v>695.9378423917098</v>
       </c>
       <c r="D22">
-        <v>851.8414883098166</v>
+        <v>853.2008423917098</v>
       </c>
       <c r="E22">
-        <v>-94.13999999999999</v>
+        <v>-86.03699999999998</v>
       </c>
       <c r="F22">
-        <v>162.06</v>
+        <v>170.163</v>
       </c>
       <c r="G22">
         <v>12.9</v>
@@ -3079,28 +3079,28 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M22">
-        <v>8.670209999999999</v>
+        <v>9.1037205</v>
       </c>
       <c r="N22">
-        <v>69.44407571428573</v>
+        <v>69.01056521428573</v>
       </c>
       <c r="O22">
-        <v>10.41661135714286</v>
+        <v>10.35158478214286</v>
       </c>
       <c r="P22">
-        <v>59.02746435714288</v>
+        <v>58.65898043214288</v>
       </c>
       <c r="Q22">
-        <v>111.6274643571429</v>
+        <v>111.2589804321429</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.13527851900473</v>
+        <v>0.1362710381376286</v>
       </c>
       <c r="T22">
-        <v>1.166205061601708</v>
+        <v>1.179140913126717</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>9.009503312409473</v>
+        <v>8.580479345151879</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1172038701287266</v>
+        <v>0.1170899250536692</v>
       </c>
       <c r="C23">
-        <v>695.9378423917099</v>
+        <v>689.198541875924</v>
       </c>
       <c r="D23">
-        <v>853.2008423917099</v>
+        <v>854.564541875924</v>
       </c>
       <c r="E23">
-        <v>-86.03700000000001</v>
+        <v>-77.934</v>
       </c>
       <c r="F23">
-        <v>170.163</v>
+        <v>178.266</v>
       </c>
       <c r="G23">
         <v>12.9</v>
@@ -3161,28 +3161,28 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M23">
-        <v>9.1037205</v>
+        <v>9.537230999999998</v>
       </c>
       <c r="N23">
-        <v>69.01056521428573</v>
+        <v>68.57705471428574</v>
       </c>
       <c r="O23">
-        <v>10.35158478214286</v>
+        <v>10.28655820714286</v>
       </c>
       <c r="P23">
-        <v>58.65898043214288</v>
+        <v>58.29049650714288</v>
       </c>
       <c r="Q23">
-        <v>111.2589804321429</v>
+        <v>110.8904965071429</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1362710381376286</v>
+        <v>0.1372890064790631</v>
       </c>
       <c r="T23">
-        <v>1.179140913126717</v>
+        <v>1.192408453152368</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.580479345151879</v>
+        <v>8.190457556735886</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1170899250536692</v>
+        <v>0.1169759799786118</v>
       </c>
       <c r="C24">
-        <v>689.198541875924</v>
+        <v>682.4636076320214</v>
       </c>
       <c r="D24">
-        <v>854.564541875924</v>
+        <v>855.9326076320215</v>
       </c>
       <c r="E24">
-        <v>-77.934</v>
+        <v>-69.83099999999999</v>
       </c>
       <c r="F24">
-        <v>178.266</v>
+        <v>186.369</v>
       </c>
       <c r="G24">
         <v>12.9</v>
@@ -3243,28 +3243,28 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M24">
-        <v>9.537230999999998</v>
+        <v>9.970741499999999</v>
       </c>
       <c r="N24">
-        <v>68.57705471428574</v>
+        <v>68.14354421428573</v>
       </c>
       <c r="O24">
-        <v>10.28655820714286</v>
+        <v>10.22153163214286</v>
       </c>
       <c r="P24">
-        <v>58.29049650714288</v>
+        <v>57.92201258214287</v>
       </c>
       <c r="Q24">
-        <v>110.8904965071429</v>
+        <v>110.5220125821429</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1372890064790631</v>
+        <v>0.1383334155566387</v>
       </c>
       <c r="T24">
-        <v>1.192408453152368</v>
+        <v>1.206020604607256</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.190457556735886</v>
+        <v>7.834350706443019</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1169759799786118</v>
+        <v>0.1170252349035544</v>
       </c>
       <c r="C25">
-        <v>682.4636076320214</v>
+        <v>673.7686980875757</v>
       </c>
       <c r="D25">
-        <v>855.9326076320215</v>
+        <v>855.3406980875757</v>
       </c>
       <c r="E25">
-        <v>-69.83099999999999</v>
+        <v>-61.72799999999998</v>
       </c>
       <c r="F25">
-        <v>186.369</v>
+        <v>194.472</v>
       </c>
       <c r="G25">
         <v>12.9</v>
@@ -3325,45 +3325,45 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M25">
-        <v>9.970741499999999</v>
+        <v>10.5598296</v>
       </c>
       <c r="N25">
-        <v>68.14354421428573</v>
+        <v>67.55445611428573</v>
       </c>
       <c r="O25">
-        <v>10.22153163214286</v>
+        <v>10.13316841714286</v>
       </c>
       <c r="P25">
-        <v>57.92201258214287</v>
+        <v>57.42128769714287</v>
       </c>
       <c r="Q25">
-        <v>110.5220125821429</v>
+        <v>110.0212876971429</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1383334155566387</v>
+        <v>0.1394053090836242</v>
       </c>
       <c r="T25">
-        <v>1.206020604607256</v>
+        <v>1.219990970574115</v>
       </c>
       <c r="U25">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V25">
         <v>0.15</v>
       </c>
       <c r="W25">
-        <v>0.04547499999999999</v>
+        <v>0.046155</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y25">
-        <v>7.834350706443019</v>
+        <v>7.397305512797832</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1170252349035544</v>
+        <v>0.116918089828497</v>
       </c>
       <c r="C26">
-        <v>673.7686980875757</v>
+        <v>666.9543370754511</v>
       </c>
       <c r="D26">
-        <v>855.3406980875757</v>
+        <v>856.6293370754512</v>
       </c>
       <c r="E26">
-        <v>-61.72800000000001</v>
+        <v>-53.625</v>
       </c>
       <c r="F26">
-        <v>194.472</v>
+        <v>202.575</v>
       </c>
       <c r="G26">
         <v>12.9</v>
@@ -3407,28 +3407,28 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M26">
-        <v>10.5598296</v>
+        <v>10.9998225</v>
       </c>
       <c r="N26">
-        <v>67.55445611428573</v>
+        <v>67.11446321428573</v>
       </c>
       <c r="O26">
-        <v>10.13316841714286</v>
+        <v>10.06716948214286</v>
       </c>
       <c r="P26">
-        <v>57.42128769714287</v>
+        <v>57.04729373214288</v>
       </c>
       <c r="Q26">
-        <v>110.0212876971429</v>
+        <v>109.6472937321429</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1394053090836242</v>
+        <v>0.140505786437996</v>
       </c>
       <c r="T26">
-        <v>1.219990970574115</v>
+        <v>1.234333879633423</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>7.397305512797833</v>
+        <v>7.10141329228592</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.116918089828497</v>
+        <v>0.1168109447534396</v>
       </c>
       <c r="C27">
-        <v>666.9543370754511</v>
+        <v>660.1438647968608</v>
       </c>
       <c r="D27">
-        <v>856.6293370754512</v>
+        <v>857.9218647968609</v>
       </c>
       <c r="E27">
-        <v>-53.625</v>
+        <v>-45.52199999999999</v>
       </c>
       <c r="F27">
-        <v>202.575</v>
+        <v>210.678</v>
       </c>
       <c r="G27">
         <v>12.9</v>
@@ -3489,28 +3489,28 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M27">
-        <v>10.9998225</v>
+        <v>11.4398154</v>
       </c>
       <c r="N27">
-        <v>67.11446321428573</v>
+        <v>66.67447031428573</v>
       </c>
       <c r="O27">
-        <v>10.06716948214286</v>
+        <v>10.00117054714286</v>
       </c>
       <c r="P27">
-        <v>57.04729373214288</v>
+        <v>56.67329976714286</v>
       </c>
       <c r="Q27">
-        <v>109.6472937321429</v>
+        <v>109.2732997671429</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.140505786437996</v>
+        <v>0.1416360064235671</v>
       </c>
       <c r="T27">
-        <v>1.234333879633423</v>
+        <v>1.249064434883524</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>7.10141329228592</v>
+        <v>6.828282011813383</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1168109447534396</v>
+        <v>0.1167037996783822</v>
       </c>
       <c r="C28">
-        <v>660.1438647968608</v>
+        <v>653.3372988809858</v>
       </c>
       <c r="D28">
-        <v>857.9218647968609</v>
+        <v>859.2182988809859</v>
       </c>
       <c r="E28">
-        <v>-45.52199999999999</v>
+        <v>-37.41899999999998</v>
       </c>
       <c r="F28">
-        <v>210.678</v>
+        <v>218.781</v>
       </c>
       <c r="G28">
         <v>12.9</v>
@@ -3571,28 +3571,28 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M28">
-        <v>11.4398154</v>
+        <v>11.8798083</v>
       </c>
       <c r="N28">
-        <v>66.67447031428573</v>
+        <v>66.23447741428572</v>
       </c>
       <c r="O28">
-        <v>10.00117054714286</v>
+        <v>9.935171612142858</v>
       </c>
       <c r="P28">
-        <v>56.67329976714286</v>
+        <v>56.29930580214286</v>
       </c>
       <c r="Q28">
-        <v>109.2732997671429</v>
+        <v>108.8993058021429</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1416360064235671</v>
+        <v>0.1427971913402496</v>
       </c>
       <c r="T28">
-        <v>1.249064434883524</v>
+        <v>1.264198566989791</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>6.828282011813383</v>
+        <v>6.575382678042517</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1167037996783822</v>
+        <v>0.1165966546033248</v>
       </c>
       <c r="C29">
-        <v>653.3372988809858</v>
+        <v>646.5346570637294</v>
       </c>
       <c r="D29">
-        <v>859.2182988809859</v>
+        <v>860.5186570637294</v>
       </c>
       <c r="E29">
-        <v>-37.41899999999998</v>
+        <v>-29.31599999999997</v>
       </c>
       <c r="F29">
-        <v>218.781</v>
+        <v>226.884</v>
       </c>
       <c r="G29">
         <v>12.9</v>
@@ -3653,28 +3653,28 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M29">
-        <v>11.8798083</v>
+        <v>12.3198012</v>
       </c>
       <c r="N29">
-        <v>66.23447741428572</v>
+        <v>65.79448451428573</v>
       </c>
       <c r="O29">
-        <v>9.935171612142858</v>
+        <v>9.869172677142858</v>
       </c>
       <c r="P29">
-        <v>56.29930580214286</v>
+        <v>55.92531183714287</v>
       </c>
       <c r="Q29">
-        <v>108.8993058021429</v>
+        <v>108.5253118371429</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1427971913402496</v>
+        <v>0.1439906313935067</v>
       </c>
       <c r="T29">
-        <v>1.264198566989791</v>
+        <v>1.279753091654567</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>6.575382678042517</v>
+        <v>6.340547582398142</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1165966546033248</v>
+        <v>0.1164895095282674</v>
       </c>
       <c r="C30">
-        <v>646.5346570637294</v>
+        <v>639.735957188524</v>
       </c>
       <c r="D30">
-        <v>860.5186570637294</v>
+        <v>861.822957188524</v>
       </c>
       <c r="E30">
-        <v>-29.31599999999997</v>
+        <v>-21.21299999999997</v>
       </c>
       <c r="F30">
-        <v>226.884</v>
+        <v>234.987</v>
       </c>
       <c r="G30">
         <v>12.9</v>
@@ -3735,28 +3735,28 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M30">
-        <v>12.3198012</v>
+        <v>12.7597941</v>
       </c>
       <c r="N30">
-        <v>65.79448451428573</v>
+        <v>65.35449161428572</v>
       </c>
       <c r="O30">
-        <v>9.869172677142858</v>
+        <v>9.803173742142858</v>
       </c>
       <c r="P30">
-        <v>55.92531183714287</v>
+        <v>55.55131787214286</v>
       </c>
       <c r="Q30">
-        <v>108.5253118371429</v>
+        <v>108.1513178721429</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1439906313935067</v>
+        <v>0.145217689476433</v>
       </c>
       <c r="T30">
-        <v>1.279753091654567</v>
+        <v>1.295745771943701</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>6.340547582398142</v>
+        <v>6.121908010591308</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1164895095282674</v>
+        <v>0.11663736445321</v>
       </c>
       <c r="C31">
-        <v>639.735957188524</v>
+        <v>629.8341216497868</v>
       </c>
       <c r="D31">
-        <v>861.822957188524</v>
+        <v>860.0241216497867</v>
       </c>
       <c r="E31">
-        <v>-21.21300000000002</v>
+        <v>-13.11000000000001</v>
       </c>
       <c r="F31">
-        <v>234.987</v>
+        <v>243.09</v>
       </c>
       <c r="G31">
         <v>12.9</v>
@@ -3817,45 +3817,45 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M31">
-        <v>12.7597941</v>
+        <v>13.442877</v>
       </c>
       <c r="N31">
-        <v>65.35449161428573</v>
+        <v>64.67140871428573</v>
       </c>
       <c r="O31">
-        <v>9.80317374214286</v>
+        <v>9.700711307142859</v>
       </c>
       <c r="P31">
-        <v>55.55131787214287</v>
+        <v>54.97069740714287</v>
       </c>
       <c r="Q31">
-        <v>108.1513178721429</v>
+        <v>107.5706974071429</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.145217689476433</v>
+        <v>0.1464798063617286</v>
       </c>
       <c r="T31">
-        <v>1.295745771943701</v>
+        <v>1.312195385955383</v>
       </c>
       <c r="U31">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V31">
         <v>0.15</v>
       </c>
       <c r="W31">
-        <v>0.046155</v>
+        <v>0.047005</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y31">
-        <v>6.12190801059131</v>
+        <v>5.810830948931969</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.11663736445321</v>
+        <v>0.1165387193781526</v>
       </c>
       <c r="C32">
-        <v>629.8341216497868</v>
+        <v>622.930424447139</v>
       </c>
       <c r="D32">
-        <v>860.0241216497867</v>
+        <v>861.223424447139</v>
       </c>
       <c r="E32">
-        <v>-13.11000000000001</v>
+        <v>-5.007000000000005</v>
       </c>
       <c r="F32">
-        <v>243.09</v>
+        <v>251.193</v>
       </c>
       <c r="G32">
         <v>12.9</v>
@@ -3899,28 +3899,28 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M32">
-        <v>13.442877</v>
+        <v>13.8909729</v>
       </c>
       <c r="N32">
-        <v>64.67140871428573</v>
+        <v>64.22331281428573</v>
       </c>
       <c r="O32">
-        <v>9.700711307142859</v>
+        <v>9.633496922142859</v>
       </c>
       <c r="P32">
-        <v>54.97069740714287</v>
+        <v>54.58981589214287</v>
       </c>
       <c r="Q32">
-        <v>107.5706974071429</v>
+        <v>107.1898158921429</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1464798063617286</v>
+        <v>0.1477785063451487</v>
       </c>
       <c r="T32">
-        <v>1.312195385955383</v>
+        <v>1.3291218003732</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.810830948931969</v>
+        <v>5.623384789289002</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1165387193781526</v>
+        <v>0.1164400743030952</v>
       </c>
       <c r="C33">
-        <v>622.930424447139</v>
+        <v>616.0300767685571</v>
       </c>
       <c r="D33">
-        <v>861.223424447139</v>
+        <v>862.4260767685572</v>
       </c>
       <c r="E33">
-        <v>-5.007000000000005</v>
+        <v>3.096000000000004</v>
       </c>
       <c r="F33">
-        <v>251.193</v>
+        <v>259.296</v>
       </c>
       <c r="G33">
         <v>12.9</v>
@@ -3981,28 +3981,28 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M33">
-        <v>13.8909729</v>
+        <v>14.3390688</v>
       </c>
       <c r="N33">
-        <v>64.22331281428573</v>
+        <v>63.77521691428573</v>
       </c>
       <c r="O33">
-        <v>9.633496922142859</v>
+        <v>9.566282537142859</v>
       </c>
       <c r="P33">
-        <v>54.58981589214287</v>
+        <v>54.20893437714287</v>
       </c>
       <c r="Q33">
-        <v>107.1898158921429</v>
+        <v>106.8089343771429</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1477785063451487</v>
+        <v>0.1491154033869047</v>
       </c>
       <c r="T33">
-        <v>1.3291218003732</v>
+        <v>1.346546050509189</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.623384789289002</v>
+        <v>5.44765401462372</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1164400743030952</v>
+        <v>0.1163414292280378</v>
       </c>
       <c r="C34">
-        <v>616.0300767685571</v>
+        <v>609.1330926659566</v>
       </c>
       <c r="D34">
-        <v>862.4260767685572</v>
+        <v>863.6320926659566</v>
       </c>
       <c r="E34">
-        <v>3.096000000000004</v>
+        <v>11.19900000000001</v>
       </c>
       <c r="F34">
-        <v>259.296</v>
+        <v>267.399</v>
       </c>
       <c r="G34">
         <v>12.9</v>
@@ -4063,28 +4063,28 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M34">
-        <v>14.3390688</v>
+        <v>14.7871647</v>
       </c>
       <c r="N34">
-        <v>63.77521691428573</v>
+        <v>63.32712101428573</v>
       </c>
       <c r="O34">
-        <v>9.566282537142859</v>
+        <v>9.499068152142859</v>
       </c>
       <c r="P34">
-        <v>54.20893437714287</v>
+        <v>53.82805286214287</v>
       </c>
       <c r="Q34">
-        <v>106.8089343771429</v>
+        <v>106.4280528621429</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1491154033869047</v>
+        <v>0.1504922078030415</v>
       </c>
       <c r="T34">
-        <v>1.346546050509189</v>
+        <v>1.364490427514908</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.44765401462372</v>
+        <v>5.282573589938153</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1163414292280378</v>
+        <v>0.1162427841529804</v>
       </c>
       <c r="C35">
-        <v>609.1330926659566</v>
+        <v>602.2394862699628</v>
       </c>
       <c r="D35">
-        <v>863.6320926659566</v>
+        <v>864.8414862699628</v>
       </c>
       <c r="E35">
-        <v>11.19900000000001</v>
+        <v>19.30200000000002</v>
       </c>
       <c r="F35">
-        <v>267.399</v>
+        <v>275.502</v>
       </c>
       <c r="G35">
         <v>12.9</v>
@@ -4145,28 +4145,28 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M35">
-        <v>14.7871647</v>
+        <v>15.2352606</v>
       </c>
       <c r="N35">
-        <v>63.32712101428573</v>
+        <v>62.87902511428572</v>
       </c>
       <c r="O35">
-        <v>9.499068152142859</v>
+        <v>9.431853767142858</v>
       </c>
       <c r="P35">
-        <v>53.82805286214287</v>
+        <v>53.44717134714287</v>
       </c>
       <c r="Q35">
-        <v>106.4280528621429</v>
+        <v>106.0471713471429</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1504922078030415</v>
+        <v>0.1519107335651219</v>
       </c>
       <c r="T35">
-        <v>1.364490427514908</v>
+        <v>1.382978573520801</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.282573589938153</v>
+        <v>5.127203778469383</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1162427841529804</v>
+        <v>0.116144139077923</v>
       </c>
       <c r="C36">
-        <v>602.2394862699628</v>
+        <v>595.3492717904643</v>
       </c>
       <c r="D36">
-        <v>864.8414862699628</v>
+        <v>866.0542717904643</v>
       </c>
       <c r="E36">
-        <v>19.30200000000002</v>
+        <v>27.40500000000003</v>
       </c>
       <c r="F36">
-        <v>275.502</v>
+        <v>283.605</v>
       </c>
       <c r="G36">
         <v>12.9</v>
@@ -4227,28 +4227,28 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M36">
-        <v>15.2352606</v>
+        <v>15.6833565</v>
       </c>
       <c r="N36">
-        <v>62.87902511428572</v>
+        <v>62.43092921428573</v>
       </c>
       <c r="O36">
-        <v>9.431853767142858</v>
+        <v>9.364639382142858</v>
       </c>
       <c r="P36">
-        <v>53.44717134714287</v>
+        <v>53.06628983214287</v>
       </c>
       <c r="Q36">
-        <v>106.0471713471429</v>
+        <v>105.6662898321429</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1519107335651219</v>
+        <v>0.1533729062737277</v>
       </c>
       <c r="T36">
-        <v>1.382978573520801</v>
+        <v>1.402035585557645</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.127203778469383</v>
+        <v>4.980712241941687</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.116144139077923</v>
+        <v>0.1160454940028656</v>
       </c>
       <c r="C37">
-        <v>595.3492717904643</v>
+        <v>588.462463517169</v>
       </c>
       <c r="D37">
-        <v>866.0542717904643</v>
+        <v>867.2704635171691</v>
       </c>
       <c r="E37">
-        <v>27.40500000000003</v>
+        <v>35.50800000000004</v>
       </c>
       <c r="F37">
-        <v>283.605</v>
+        <v>291.708</v>
       </c>
       <c r="G37">
         <v>12.9</v>
@@ -4309,28 +4309,28 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M37">
-        <v>15.6833565</v>
+        <v>16.1314524</v>
       </c>
       <c r="N37">
-        <v>62.43092921428573</v>
+        <v>61.98283331428573</v>
       </c>
       <c r="O37">
-        <v>9.364639382142858</v>
+        <v>9.297424997142858</v>
       </c>
       <c r="P37">
-        <v>53.06628983214287</v>
+        <v>52.68540831714287</v>
       </c>
       <c r="Q37">
-        <v>105.6662898321429</v>
+        <v>105.2854083171429</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1533729062737277</v>
+        <v>0.1548807718794775</v>
       </c>
       <c r="T37">
-        <v>1.402035585557645</v>
+        <v>1.421688129220639</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.980712241941687</v>
+        <v>4.842359124109973</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1160454940028656</v>
+        <v>0.1159468489278082</v>
       </c>
       <c r="C38">
-        <v>588.4624635171688</v>
+        <v>581.5790758201642</v>
       </c>
       <c r="D38">
-        <v>867.2704635171688</v>
+        <v>868.4900758201642</v>
       </c>
       <c r="E38">
-        <v>35.50799999999998</v>
+        <v>43.61099999999999</v>
       </c>
       <c r="F38">
-        <v>291.708</v>
+        <v>299.811</v>
       </c>
       <c r="G38">
         <v>12.9</v>
@@ -4391,28 +4391,28 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M38">
-        <v>16.1314524</v>
+        <v>16.5795483</v>
       </c>
       <c r="N38">
-        <v>61.98283331428573</v>
+        <v>61.53473741428573</v>
       </c>
       <c r="O38">
-        <v>9.297424997142858</v>
+        <v>9.230210612142859</v>
       </c>
       <c r="P38">
-        <v>52.68540831714287</v>
+        <v>52.30452680214287</v>
       </c>
       <c r="Q38">
-        <v>105.2854083171429</v>
+        <v>104.9045268021429</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1548807718794775</v>
+        <v>0.1564365062346162</v>
       </c>
       <c r="T38">
-        <v>1.421688129220639</v>
+        <v>1.44196456315865</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.842359124109973</v>
+        <v>4.711484553188082</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1159468489278082</v>
+        <v>0.1158482038527508</v>
       </c>
       <c r="C39">
-        <v>581.5790758201642</v>
+        <v>574.6991231504853</v>
       </c>
       <c r="D39">
-        <v>868.4900758201642</v>
+        <v>869.7131231504853</v>
       </c>
       <c r="E39">
-        <v>43.61099999999999</v>
+        <v>51.714</v>
       </c>
       <c r="F39">
-        <v>299.811</v>
+        <v>307.914</v>
       </c>
       <c r="G39">
         <v>12.9</v>
@@ -4473,28 +4473,28 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M39">
-        <v>16.5795483</v>
+        <v>17.0276442</v>
       </c>
       <c r="N39">
-        <v>61.53473741428573</v>
+        <v>61.08664151428573</v>
       </c>
       <c r="O39">
-        <v>9.230210612142859</v>
+        <v>9.162996227142859</v>
       </c>
       <c r="P39">
-        <v>52.30452680214287</v>
+        <v>51.92364528714288</v>
       </c>
       <c r="Q39">
-        <v>104.9045268021429</v>
+        <v>104.5236452871429</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1564365062346162</v>
+        <v>0.158042425568953</v>
       </c>
       <c r="T39">
-        <v>1.44196456315865</v>
+        <v>1.462895075610789</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.711484553188082</v>
+        <v>4.587498117577869</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1158482038527508</v>
+        <v>0.1165783087776934</v>
       </c>
       <c r="C40">
-        <v>574.6991231504853</v>
+        <v>557.6247045694931</v>
       </c>
       <c r="D40">
-        <v>869.7131231504853</v>
+        <v>860.7417045694931</v>
       </c>
       <c r="E40">
-        <v>51.714</v>
+        <v>59.81700000000001</v>
       </c>
       <c r="F40">
-        <v>307.914</v>
+        <v>316.017</v>
       </c>
       <c r="G40">
         <v>12.9</v>
@@ -4555,45 +4555,45 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M40">
-        <v>17.0276442</v>
+        <v>18.2657826</v>
       </c>
       <c r="N40">
-        <v>61.08664151428573</v>
+        <v>59.84850311428573</v>
       </c>
       <c r="O40">
-        <v>9.162996227142859</v>
+        <v>8.977275467142858</v>
       </c>
       <c r="P40">
-        <v>51.92364528714288</v>
+        <v>50.87122764714287</v>
       </c>
       <c r="Q40">
-        <v>104.5236452871429</v>
+        <v>103.4712276471429</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.158042425568953</v>
+        <v>0.1597009979962188</v>
       </c>
       <c r="T40">
-        <v>1.462895075610789</v>
+        <v>1.484511834372835</v>
       </c>
       <c r="U40">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V40">
         <v>0.15</v>
       </c>
       <c r="W40">
-        <v>0.047005</v>
+        <v>0.04913</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y40">
-        <v>4.587498117577869</v>
+        <v>4.276536484907344</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1165783087776934</v>
+        <v>0.116500913702636</v>
       </c>
       <c r="C41">
-        <v>557.6247045694931</v>
+        <v>550.4639437194761</v>
       </c>
       <c r="D41">
-        <v>860.7417045694931</v>
+        <v>861.6839437194761</v>
       </c>
       <c r="E41">
-        <v>59.81700000000001</v>
+        <v>67.92000000000002</v>
       </c>
       <c r="F41">
-        <v>316.017</v>
+        <v>324.12</v>
       </c>
       <c r="G41">
         <v>12.9</v>
@@ -4637,28 +4637,28 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M41">
-        <v>18.2657826</v>
+        <v>18.734136</v>
       </c>
       <c r="N41">
-        <v>59.84850311428573</v>
+        <v>59.38014971428572</v>
       </c>
       <c r="O41">
-        <v>8.977275467142858</v>
+        <v>8.907022457142858</v>
       </c>
       <c r="P41">
-        <v>50.87122764714287</v>
+        <v>50.47312725714286</v>
       </c>
       <c r="Q41">
-        <v>103.4712276471429</v>
+        <v>103.0731272571429</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1597009979962188</v>
+        <v>0.1614148561710601</v>
       </c>
       <c r="T41">
-        <v>1.484511834372835</v>
+        <v>1.506849151760283</v>
       </c>
       <c r="U41">
         <v>0.0578</v>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.276536484907344</v>
+        <v>4.16962307278466</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.116500913702636</v>
+        <v>0.1164235186275786</v>
       </c>
       <c r="C42">
-        <v>550.4639437194761</v>
+        <v>543.3052480361673</v>
       </c>
       <c r="D42">
-        <v>861.6839437194761</v>
+        <v>862.6282480361673</v>
       </c>
       <c r="E42">
-        <v>67.92000000000002</v>
+        <v>76.02300000000002</v>
       </c>
       <c r="F42">
-        <v>324.12</v>
+        <v>332.223</v>
       </c>
       <c r="G42">
         <v>12.9</v>
@@ -4719,28 +4719,28 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M42">
-        <v>18.734136</v>
+        <v>19.2024894</v>
       </c>
       <c r="N42">
-        <v>59.38014971428572</v>
+        <v>58.91179631428572</v>
       </c>
       <c r="O42">
-        <v>8.907022457142858</v>
+        <v>8.836769447142858</v>
       </c>
       <c r="P42">
-        <v>50.47312725714286</v>
+        <v>50.07502686714287</v>
       </c>
       <c r="Q42">
-        <v>103.0731272571429</v>
+        <v>102.6750268671429</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1614148561710601</v>
+        <v>0.1631868112331841</v>
       </c>
       <c r="T42">
-        <v>1.506849151760283</v>
+        <v>1.529943666347305</v>
       </c>
       <c r="U42">
         <v>0.0578</v>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.16962307278466</v>
+        <v>4.067924949058205</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1164235186275786</v>
+        <v>0.1175956235525212</v>
       </c>
       <c r="C43">
-        <v>543.3052480361673</v>
+        <v>521.1193448188403</v>
       </c>
       <c r="D43">
-        <v>862.6282480361673</v>
+        <v>848.5453448188404</v>
       </c>
       <c r="E43">
-        <v>76.02300000000002</v>
+        <v>84.12600000000003</v>
       </c>
       <c r="F43">
-        <v>332.223</v>
+        <v>340.326</v>
       </c>
       <c r="G43">
         <v>12.9</v>
@@ -4801,45 +4801,45 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M43">
-        <v>19.2024894</v>
+        <v>20.8619838</v>
       </c>
       <c r="N43">
-        <v>58.91179631428572</v>
+        <v>57.25230191428572</v>
       </c>
       <c r="O43">
-        <v>8.836769447142858</v>
+        <v>8.587845287142859</v>
       </c>
       <c r="P43">
-        <v>50.07502686714287</v>
+        <v>48.66445662714287</v>
       </c>
       <c r="Q43">
-        <v>102.6750268671429</v>
+        <v>101.2644566271429</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1631868112331841</v>
+        <v>0.1650198681940021</v>
       </c>
       <c r="T43">
-        <v>1.529943666347305</v>
+        <v>1.553834543506293</v>
       </c>
       <c r="U43">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V43">
         <v>0.15</v>
       </c>
       <c r="W43">
-        <v>0.04913</v>
+        <v>0.052105</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y43">
-        <v>4.067924949058205</v>
+        <v>3.744336418969212</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1175956235525212</v>
+        <v>0.1175479784774638</v>
       </c>
       <c r="C44">
-        <v>521.1193448188399</v>
+        <v>513.579831170671</v>
       </c>
       <c r="D44">
-        <v>848.5453448188399</v>
+        <v>849.108831170671</v>
       </c>
       <c r="E44">
-        <v>84.12599999999998</v>
+        <v>92.22899999999998</v>
       </c>
       <c r="F44">
-        <v>340.326</v>
+        <v>348.429</v>
       </c>
       <c r="G44">
         <v>12.9</v>
@@ -4883,28 +4883,28 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M44">
-        <v>20.8619838</v>
+        <v>21.3586977</v>
       </c>
       <c r="N44">
-        <v>57.25230191428573</v>
+        <v>56.75558801428573</v>
       </c>
       <c r="O44">
-        <v>8.587845287142859</v>
+        <v>8.51333820214286</v>
       </c>
       <c r="P44">
-        <v>48.66445662714287</v>
+        <v>48.24224981214287</v>
       </c>
       <c r="Q44">
-        <v>101.2644566271429</v>
+        <v>100.8422498121429</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1650198681940021</v>
+        <v>0.166917242942919</v>
       </c>
       <c r="T44">
-        <v>1.553834543506293</v>
+        <v>1.578563697056825</v>
       </c>
       <c r="U44">
         <v>0.0613</v>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.744336418969213</v>
+        <v>3.657258827830395</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1175479784774638</v>
+        <v>0.1175003334024065</v>
       </c>
       <c r="C45">
-        <v>513.579831170671</v>
+        <v>506.0410663990619</v>
       </c>
       <c r="D45">
-        <v>849.108831170671</v>
+        <v>849.6730663990619</v>
       </c>
       <c r="E45">
-        <v>92.22899999999998</v>
+        <v>100.332</v>
       </c>
       <c r="F45">
-        <v>348.429</v>
+        <v>356.532</v>
       </c>
       <c r="G45">
         <v>12.9</v>
@@ -4965,28 +4965,28 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M45">
-        <v>21.3586977</v>
+        <v>21.8554116</v>
       </c>
       <c r="N45">
-        <v>56.75558801428573</v>
+        <v>56.25887411428573</v>
       </c>
       <c r="O45">
-        <v>8.51333820214286</v>
+        <v>8.438831117142859</v>
       </c>
       <c r="P45">
-        <v>48.24224981214287</v>
+        <v>47.82004299714287</v>
       </c>
       <c r="Q45">
-        <v>100.8422498121429</v>
+        <v>100.4200429971429</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.166917242942919</v>
+        <v>0.1688823810757258</v>
       </c>
       <c r="T45">
-        <v>1.578563697056825</v>
+        <v>1.604176034662733</v>
       </c>
       <c r="U45">
         <v>0.0613</v>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.657258827830395</v>
+        <v>3.574139309016067</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1175003334024065</v>
+        <v>0.1185236883273491</v>
       </c>
       <c r="C46">
-        <v>506.0410663990619</v>
+        <v>485.9816167594805</v>
       </c>
       <c r="D46">
-        <v>849.6730663990619</v>
+        <v>837.7166167594805</v>
       </c>
       <c r="E46">
-        <v>100.332</v>
+        <v>108.435</v>
       </c>
       <c r="F46">
-        <v>356.532</v>
+        <v>364.635</v>
       </c>
       <c r="G46">
         <v>12.9</v>
@@ -5047,45 +5047,45 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M46">
-        <v>21.8554116</v>
+        <v>23.3731035</v>
       </c>
       <c r="N46">
-        <v>56.25887411428573</v>
+        <v>54.74118221428573</v>
       </c>
       <c r="O46">
-        <v>8.438831117142859</v>
+        <v>8.211177332142858</v>
       </c>
       <c r="P46">
-        <v>47.82004299714287</v>
+        <v>46.53000488214287</v>
       </c>
       <c r="Q46">
-        <v>100.4200429971429</v>
+        <v>99.13000488214286</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1688823810757258</v>
+        <v>0.1709189787769983</v>
       </c>
       <c r="T46">
-        <v>1.604176034662733</v>
+        <v>1.630719729999764</v>
       </c>
       <c r="U46">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V46">
         <v>0.15</v>
       </c>
       <c r="W46">
-        <v>0.052105</v>
+        <v>0.054485</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y46">
-        <v>3.574139309016067</v>
+        <v>3.342058777700861</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1185236883273491</v>
+        <v>0.1184998432522917</v>
       </c>
       <c r="C47">
-        <v>485.9816167594805</v>
+        <v>478.1533823533227</v>
       </c>
       <c r="D47">
-        <v>837.7166167594805</v>
+        <v>837.9913823533227</v>
       </c>
       <c r="E47">
-        <v>108.435</v>
+        <v>116.538</v>
       </c>
       <c r="F47">
-        <v>364.635</v>
+        <v>372.738</v>
       </c>
       <c r="G47">
         <v>12.9</v>
@@ -5129,28 +5129,28 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M47">
-        <v>23.3731035</v>
+        <v>23.8925058</v>
       </c>
       <c r="N47">
-        <v>54.74118221428573</v>
+        <v>54.22177991428573</v>
       </c>
       <c r="O47">
-        <v>8.211177332142858</v>
+        <v>8.133266987142859</v>
       </c>
       <c r="P47">
-        <v>46.53000488214287</v>
+        <v>46.08851292714287</v>
       </c>
       <c r="Q47">
-        <v>99.13000488214286</v>
+        <v>98.68851292714285</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1709189787769983</v>
+        <v>0.1730310060227623</v>
       </c>
       <c r="T47">
-        <v>1.630719729999764</v>
+        <v>1.658246525164094</v>
       </c>
       <c r="U47">
         <v>0.0641</v>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.342058777700861</v>
+        <v>3.269405326011712</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1184998432522917</v>
+        <v>0.1184759981772343</v>
       </c>
       <c r="C48">
-        <v>478.1533823533227</v>
+        <v>470.325328248953</v>
       </c>
       <c r="D48">
-        <v>837.9913823533227</v>
+        <v>838.2663282489531</v>
       </c>
       <c r="E48">
-        <v>116.538</v>
+        <v>124.641</v>
       </c>
       <c r="F48">
-        <v>372.738</v>
+        <v>380.841</v>
       </c>
       <c r="G48">
         <v>12.9</v>
@@ -5211,28 +5211,28 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M48">
-        <v>23.8925058</v>
+        <v>24.4119081</v>
       </c>
       <c r="N48">
-        <v>54.22177991428573</v>
+        <v>53.70237761428572</v>
       </c>
       <c r="O48">
-        <v>8.133266987142859</v>
+        <v>8.055356642142858</v>
       </c>
       <c r="P48">
-        <v>46.08851292714287</v>
+        <v>45.64702097214287</v>
       </c>
       <c r="Q48">
-        <v>98.68851292714285</v>
+        <v>98.24702097214286</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1730310060227623</v>
+        <v>0.175222732409876</v>
       </c>
       <c r="T48">
-        <v>1.658246525164094</v>
+        <v>1.686812067315756</v>
       </c>
       <c r="U48">
         <v>0.0641</v>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.269405326011712</v>
+        <v>3.199843510564654</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1184759981772343</v>
+        <v>0.1184521531021769</v>
       </c>
       <c r="C49">
-        <v>470.325328248953</v>
+        <v>462.4974546239014</v>
       </c>
       <c r="D49">
-        <v>838.2663282489531</v>
+        <v>838.5414546239015</v>
       </c>
       <c r="E49">
-        <v>124.641</v>
+        <v>132.744</v>
       </c>
       <c r="F49">
-        <v>380.841</v>
+        <v>388.944</v>
       </c>
       <c r="G49">
         <v>12.9</v>
@@ -5293,28 +5293,28 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M49">
-        <v>24.4119081</v>
+        <v>24.9313104</v>
       </c>
       <c r="N49">
-        <v>53.70237761428572</v>
+        <v>53.18297531428573</v>
       </c>
       <c r="O49">
-        <v>8.055356642142858</v>
+        <v>7.977446297142858</v>
       </c>
       <c r="P49">
-        <v>45.64702097214287</v>
+        <v>45.20552901714287</v>
       </c>
       <c r="Q49">
-        <v>98.24702097214286</v>
+        <v>97.80552901714286</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.175222732409876</v>
+        <v>0.1774987559657247</v>
       </c>
       <c r="T49">
-        <v>1.686812067315756</v>
+        <v>1.716476284165559</v>
       </c>
       <c r="U49">
         <v>0.0641</v>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.199843510564654</v>
+        <v>3.133180104094558</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1184521531021769</v>
+        <v>0.1184283080271195</v>
       </c>
       <c r="C50">
-        <v>462.4974546239015</v>
+        <v>454.6697616559307</v>
       </c>
       <c r="D50">
-        <v>838.5414546239015</v>
+        <v>838.8167616559307</v>
       </c>
       <c r="E50">
-        <v>132.744</v>
+        <v>140.847</v>
       </c>
       <c r="F50">
-        <v>388.944</v>
+        <v>397.047</v>
       </c>
       <c r="G50">
         <v>12.9</v>
@@ -5375,28 +5375,28 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M50">
-        <v>24.9313104</v>
+        <v>25.4507127</v>
       </c>
       <c r="N50">
-        <v>53.18297531428573</v>
+        <v>52.66357301428573</v>
       </c>
       <c r="O50">
-        <v>7.977446297142858</v>
+        <v>7.899535952142859</v>
       </c>
       <c r="P50">
-        <v>45.20552901714287</v>
+        <v>44.76403706214288</v>
       </c>
       <c r="Q50">
-        <v>97.80552901714286</v>
+        <v>97.36403706214287</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1774987559657247</v>
+        <v>0.179864035347293</v>
       </c>
       <c r="T50">
-        <v>1.716476284165559</v>
+        <v>1.747303803636923</v>
       </c>
       <c r="U50">
         <v>0.0641</v>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.133180104094558</v>
+        <v>3.069237652990587</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1184283080271195</v>
+        <v>0.1184044629520621</v>
       </c>
       <c r="C51">
-        <v>454.6697616559307</v>
+        <v>446.8422495230373</v>
       </c>
       <c r="D51">
-        <v>838.8167616559307</v>
+        <v>839.0922495230373</v>
       </c>
       <c r="E51">
-        <v>140.847</v>
+        <v>148.95</v>
       </c>
       <c r="F51">
-        <v>397.047</v>
+        <v>405.15</v>
       </c>
       <c r="G51">
         <v>12.9</v>
@@ -5457,28 +5457,28 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M51">
-        <v>25.4507127</v>
+        <v>25.970115</v>
       </c>
       <c r="N51">
-        <v>52.66357301428573</v>
+        <v>52.14417071428573</v>
       </c>
       <c r="O51">
-        <v>7.899535952142859</v>
+        <v>7.821625607142859</v>
       </c>
       <c r="P51">
-        <v>44.76403706214288</v>
+        <v>44.32254510714287</v>
       </c>
       <c r="Q51">
-        <v>97.36403706214287</v>
+        <v>96.92254510714287</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.179864035347293</v>
+        <v>0.1823239259041241</v>
       </c>
       <c r="T51">
-        <v>1.747303803636923</v>
+        <v>1.779364423887142</v>
       </c>
       <c r="U51">
         <v>0.0641</v>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.069237652990587</v>
+        <v>3.007852899930775</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1184044629520621</v>
+        <v>0.1217619178770047</v>
       </c>
       <c r="C52">
-        <v>446.8422495230373</v>
+        <v>401.6520552501932</v>
       </c>
       <c r="D52">
-        <v>839.0922495230373</v>
+        <v>802.0050552501932</v>
       </c>
       <c r="E52">
-        <v>148.95</v>
+        <v>157.053</v>
       </c>
       <c r="F52">
-        <v>405.15</v>
+        <v>413.253</v>
       </c>
       <c r="G52">
         <v>12.9</v>
@@ -5539,45 +5539,45 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M52">
-        <v>25.970115</v>
+        <v>29.7128907</v>
       </c>
       <c r="N52">
-        <v>52.14417071428573</v>
+        <v>48.40139501428573</v>
       </c>
       <c r="O52">
-        <v>7.821625607142859</v>
+        <v>7.260209252142858</v>
       </c>
       <c r="P52">
-        <v>44.32254510714287</v>
+        <v>41.14118576214287</v>
       </c>
       <c r="Q52">
-        <v>96.92254510714287</v>
+        <v>93.74118576214286</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1823239259041241</v>
+        <v>0.1848842201571524</v>
       </c>
       <c r="T52">
-        <v>1.779364423887142</v>
+        <v>1.812733640882268</v>
       </c>
       <c r="U52">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V52">
         <v>0.15</v>
       </c>
       <c r="W52">
-        <v>0.054485</v>
+        <v>0.061115</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y52">
-        <v>3.007852899930775</v>
+        <v>2.628969577648186</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1217619178770047</v>
+        <v>0.1218043728019473</v>
       </c>
       <c r="C53">
-        <v>401.6520552501932</v>
+        <v>393.1010670204507</v>
       </c>
       <c r="D53">
-        <v>802.0050552501932</v>
+        <v>801.5570670204507</v>
       </c>
       <c r="E53">
-        <v>157.053</v>
+        <v>165.156</v>
       </c>
       <c r="F53">
-        <v>413.253</v>
+        <v>421.356</v>
       </c>
       <c r="G53">
         <v>12.9</v>
@@ -5621,28 +5621,28 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M53">
-        <v>29.7128907</v>
+        <v>30.2954964</v>
       </c>
       <c r="N53">
-        <v>48.40139501428573</v>
+        <v>47.81878931428572</v>
       </c>
       <c r="O53">
-        <v>7.260209252142858</v>
+        <v>7.172818397142859</v>
       </c>
       <c r="P53">
-        <v>41.14118576214287</v>
+        <v>40.64597091714286</v>
       </c>
       <c r="Q53">
-        <v>93.74118576214286</v>
+        <v>93.24597091714286</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1848842201571524</v>
+        <v>0.1875511933373901</v>
       </c>
       <c r="T53">
-        <v>1.812733640882268</v>
+        <v>1.847493241918857</v>
       </c>
       <c r="U53">
         <v>0.07190000000000001</v>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.628969577648186</v>
+        <v>2.578412470385721</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1218043728019473</v>
+        <v>0.1218468277268899</v>
       </c>
       <c r="C54">
-        <v>393.1010670204507</v>
+        <v>384.5505789905782</v>
       </c>
       <c r="D54">
-        <v>801.5570670204507</v>
+        <v>801.1095789905783</v>
       </c>
       <c r="E54">
-        <v>165.156</v>
+        <v>173.259</v>
       </c>
       <c r="F54">
-        <v>421.356</v>
+        <v>429.459</v>
       </c>
       <c r="G54">
         <v>12.9</v>
@@ -5703,28 +5703,28 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M54">
-        <v>30.2954964</v>
+        <v>30.8781021</v>
       </c>
       <c r="N54">
-        <v>47.81878931428572</v>
+        <v>47.23618361428572</v>
       </c>
       <c r="O54">
-        <v>7.172818397142859</v>
+        <v>7.085427542142858</v>
       </c>
       <c r="P54">
-        <v>40.64597091714286</v>
+        <v>40.15075607214286</v>
       </c>
       <c r="Q54">
-        <v>93.24597091714286</v>
+        <v>92.75075607214285</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1875511933373901</v>
+        <v>0.1903316547380635</v>
       </c>
       <c r="T54">
-        <v>1.847493241918857</v>
+        <v>1.88373197491445</v>
       </c>
       <c r="U54">
         <v>0.07190000000000001</v>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.578412470385721</v>
+        <v>2.529763178491651</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1218468277268899</v>
+        <v>0.1236793826518325</v>
       </c>
       <c r="C55">
-        <v>384.5505789905782</v>
+        <v>357.5969248840726</v>
       </c>
       <c r="D55">
-        <v>801.1095789905783</v>
+        <v>782.2589248840726</v>
       </c>
       <c r="E55">
-        <v>173.259</v>
+        <v>181.362</v>
       </c>
       <c r="F55">
-        <v>429.459</v>
+        <v>437.562</v>
       </c>
       <c r="G55">
         <v>12.9</v>
@@ -5785,45 +5785,45 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M55">
-        <v>30.8781021</v>
+        <v>33.1671996</v>
       </c>
       <c r="N55">
-        <v>47.23618361428572</v>
+        <v>44.94708611428572</v>
       </c>
       <c r="O55">
-        <v>7.085427542142858</v>
+        <v>6.742062917142858</v>
       </c>
       <c r="P55">
-        <v>40.15075607214286</v>
+        <v>38.20502319714286</v>
       </c>
       <c r="Q55">
-        <v>92.75075607214285</v>
+        <v>90.80502319714286</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1903316547380635</v>
+        <v>0.1932330057648532</v>
       </c>
       <c r="T55">
-        <v>1.88373197491445</v>
+        <v>1.921546304996808</v>
       </c>
       <c r="U55">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V55">
         <v>0.15</v>
       </c>
       <c r="W55">
-        <v>0.061115</v>
+        <v>0.06443</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y55">
-        <v>2.529763178491651</v>
+        <v>2.355166750776442</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1236793826518325</v>
+        <v>0.1237549875767751</v>
       </c>
       <c r="C56">
-        <v>357.5969248840726</v>
+        <v>348.7352482536224</v>
       </c>
       <c r="D56">
-        <v>782.2589248840726</v>
+        <v>781.5002482536224</v>
       </c>
       <c r="E56">
-        <v>181.362</v>
+        <v>189.465</v>
       </c>
       <c r="F56">
-        <v>437.562</v>
+        <v>445.665</v>
       </c>
       <c r="G56">
         <v>12.9</v>
@@ -5867,28 +5867,28 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M56">
-        <v>33.1671996</v>
+        <v>33.781407</v>
       </c>
       <c r="N56">
-        <v>44.94708611428572</v>
+        <v>44.33287871428573</v>
       </c>
       <c r="O56">
-        <v>6.742062917142858</v>
+        <v>6.649931807142859</v>
       </c>
       <c r="P56">
-        <v>38.20502319714286</v>
+        <v>37.68294690714287</v>
       </c>
       <c r="Q56">
-        <v>90.80502319714286</v>
+        <v>90.28294690714287</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1932330057648532</v>
+        <v>0.1962633057261668</v>
       </c>
       <c r="T56">
-        <v>1.921546304996808</v>
+        <v>1.961041271971716</v>
       </c>
       <c r="U56">
         <v>0.07580000000000001</v>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.355166750776442</v>
+        <v>2.312345537125962</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1237549875767751</v>
+        <v>0.1238305925017177</v>
       </c>
       <c r="C57">
-        <v>348.7352482536224</v>
+        <v>339.8750418078233</v>
       </c>
       <c r="D57">
-        <v>781.5002482536224</v>
+        <v>780.7430418078234</v>
       </c>
       <c r="E57">
-        <v>189.465</v>
+        <v>197.568</v>
       </c>
       <c r="F57">
-        <v>445.665</v>
+        <v>453.768</v>
       </c>
       <c r="G57">
         <v>12.9</v>
@@ -5949,28 +5949,28 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M57">
-        <v>33.781407</v>
+        <v>34.39561440000001</v>
       </c>
       <c r="N57">
-        <v>44.33287871428573</v>
+        <v>43.71867131428572</v>
       </c>
       <c r="O57">
-        <v>6.649931807142859</v>
+        <v>6.557800697142858</v>
       </c>
       <c r="P57">
-        <v>37.68294690714287</v>
+        <v>37.16087061714286</v>
       </c>
       <c r="Q57">
-        <v>90.28294690714287</v>
+        <v>89.76087061714286</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1962633057261668</v>
+        <v>0.1994313465948129</v>
       </c>
       <c r="T57">
-        <v>1.961041271971716</v>
+        <v>2.00233146471821</v>
       </c>
       <c r="U57">
         <v>0.07580000000000001</v>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.312345537125962</v>
+        <v>2.271053652534427</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1238305925017177</v>
+        <v>0.1239061974266603</v>
       </c>
       <c r="C58">
-        <v>339.8750418078233</v>
+        <v>331.0163012773642</v>
       </c>
       <c r="D58">
-        <v>780.7430418078234</v>
+        <v>779.9873012773643</v>
       </c>
       <c r="E58">
-        <v>197.568</v>
+        <v>205.671</v>
       </c>
       <c r="F58">
-        <v>453.768</v>
+        <v>461.871</v>
       </c>
       <c r="G58">
         <v>12.9</v>
@@ -6031,28 +6031,28 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M58">
-        <v>34.39561440000001</v>
+        <v>35.0098218</v>
       </c>
       <c r="N58">
-        <v>43.71867131428572</v>
+        <v>43.10446391428572</v>
       </c>
       <c r="O58">
-        <v>6.557800697142858</v>
+        <v>6.465669587142858</v>
       </c>
       <c r="P58">
-        <v>37.16087061714286</v>
+        <v>36.63879432714287</v>
       </c>
       <c r="Q58">
-        <v>89.76087061714286</v>
+        <v>89.23879432714287</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1994313465948129</v>
+        <v>0.2027467382015355</v>
       </c>
       <c r="T58">
-        <v>2.00233146471821</v>
+        <v>2.045542131545936</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.271053652534427</v>
+        <v>2.231210605998735</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1239061974266603</v>
+        <v>0.1239818023516029</v>
       </c>
       <c r="C59">
-        <v>331.0163012773642</v>
+        <v>322.1590224094501</v>
       </c>
       <c r="D59">
-        <v>779.9873012773643</v>
+        <v>779.2330224094502</v>
       </c>
       <c r="E59">
-        <v>205.671</v>
+        <v>213.7740000000001</v>
       </c>
       <c r="F59">
-        <v>461.871</v>
+        <v>469.974</v>
       </c>
       <c r="G59">
         <v>12.9</v>
@@ -6113,28 +6113,28 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M59">
-        <v>35.0098218</v>
+        <v>35.62402920000001</v>
       </c>
       <c r="N59">
-        <v>43.10446391428572</v>
+        <v>42.49025651428572</v>
       </c>
       <c r="O59">
-        <v>6.465669587142858</v>
+        <v>6.373538477142858</v>
       </c>
       <c r="P59">
-        <v>36.63879432714287</v>
+        <v>36.11671803714286</v>
       </c>
       <c r="Q59">
-        <v>89.23879432714287</v>
+        <v>88.71671803714285</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2027467382015355</v>
+        <v>0.2062200055990545</v>
       </c>
       <c r="T59">
-        <v>2.045542131545936</v>
+        <v>2.090810449174982</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.231210605998735</v>
+        <v>2.192741457619446</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1239818023516029</v>
+        <v>0.1240574072765455</v>
       </c>
       <c r="C60">
-        <v>322.1590224094504</v>
+        <v>313.3032009677193</v>
       </c>
       <c r="D60">
-        <v>779.2330224094503</v>
+        <v>778.4802009677193</v>
       </c>
       <c r="E60">
-        <v>213.7739999999999</v>
+        <v>221.877</v>
       </c>
       <c r="F60">
-        <v>469.9739999999999</v>
+        <v>478.0769999999999</v>
       </c>
       <c r="G60">
         <v>12.9</v>
@@ -6195,28 +6195,28 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M60">
-        <v>35.6240292</v>
+        <v>36.2382366</v>
       </c>
       <c r="N60">
-        <v>42.49025651428573</v>
+        <v>41.87604911428573</v>
       </c>
       <c r="O60">
-        <v>6.373538477142859</v>
+        <v>6.281407367142859</v>
       </c>
       <c r="P60">
-        <v>36.11671803714287</v>
+        <v>35.59464174714287</v>
       </c>
       <c r="Q60">
-        <v>88.71671803714287</v>
+        <v>88.19464174714287</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2062200055990545</v>
+        <v>0.2098627006745011</v>
       </c>
       <c r="T60">
-        <v>2.090810449174982</v>
+        <v>2.138286977420079</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.192741457619447</v>
+        <v>2.155576348168269</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1240574072765455</v>
+        <v>0.1241330122014881</v>
       </c>
       <c r="C61">
-        <v>313.3032009677193</v>
+        <v>304.4488327321652</v>
       </c>
       <c r="D61">
-        <v>778.4802009677193</v>
+        <v>777.7288327321652</v>
       </c>
       <c r="E61">
-        <v>221.877</v>
+        <v>229.98</v>
       </c>
       <c r="F61">
-        <v>478.0769999999999</v>
+        <v>486.1799999999999</v>
       </c>
       <c r="G61">
         <v>12.9</v>
@@ -6277,28 +6277,28 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M61">
-        <v>36.2382366</v>
+        <v>36.852444</v>
       </c>
       <c r="N61">
-        <v>41.87604911428573</v>
+        <v>41.26184171428573</v>
       </c>
       <c r="O61">
-        <v>6.281407367142859</v>
+        <v>6.189276257142859</v>
       </c>
       <c r="P61">
-        <v>35.59464174714287</v>
+        <v>35.07256545714287</v>
       </c>
       <c r="Q61">
-        <v>88.19464174714287</v>
+        <v>87.67256545714287</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2098627006745011</v>
+        <v>0.2136875305037202</v>
       </c>
       <c r="T61">
-        <v>2.138286977420079</v>
+        <v>2.188137332077432</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.155576348168269</v>
+        <v>2.119650075698798</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1241330122014881</v>
+        <v>0.1242086171264307</v>
       </c>
       <c r="C62">
-        <v>304.4488327321652</v>
+        <v>295.5959134990584</v>
       </c>
       <c r="D62">
-        <v>777.7288327321652</v>
+        <v>776.9789134990584</v>
       </c>
       <c r="E62">
-        <v>229.98</v>
+        <v>238.083</v>
       </c>
       <c r="F62">
-        <v>486.1799999999999</v>
+        <v>494.283</v>
       </c>
       <c r="G62">
         <v>12.9</v>
@@ -6359,28 +6359,28 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M62">
-        <v>36.852444</v>
+        <v>37.4666514</v>
       </c>
       <c r="N62">
-        <v>41.26184171428573</v>
+        <v>40.64763431428572</v>
       </c>
       <c r="O62">
-        <v>6.189276257142859</v>
+        <v>6.097145147142858</v>
       </c>
       <c r="P62">
-        <v>35.07256545714287</v>
+        <v>34.55048916714286</v>
       </c>
       <c r="Q62">
-        <v>87.67256545714287</v>
+        <v>87.15048916714287</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2136875305037202</v>
+        <v>0.2177085054523863</v>
       </c>
       <c r="T62">
-        <v>2.188137332077432</v>
+        <v>2.240544115178751</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.119650075698798</v>
+        <v>2.084901713802097</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1242086171264307</v>
+        <v>0.1242842220513733</v>
       </c>
       <c r="C63">
-        <v>295.5959134990584</v>
+        <v>286.7444390808674</v>
       </c>
       <c r="D63">
-        <v>776.9789134990584</v>
+        <v>776.2304390808674</v>
       </c>
       <c r="E63">
-        <v>238.083</v>
+        <v>246.186</v>
       </c>
       <c r="F63">
-        <v>494.283</v>
+        <v>502.386</v>
       </c>
       <c r="G63">
         <v>12.9</v>
@@ -6441,28 +6441,28 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M63">
-        <v>37.4666514</v>
+        <v>38.0808588</v>
       </c>
       <c r="N63">
-        <v>40.64763431428572</v>
+        <v>40.03342691428573</v>
       </c>
       <c r="O63">
-        <v>6.097145147142858</v>
+        <v>6.005014037142859</v>
       </c>
       <c r="P63">
-        <v>34.55048916714286</v>
+        <v>34.02841287714287</v>
       </c>
       <c r="Q63">
-        <v>87.15048916714287</v>
+        <v>86.62841287714286</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2177085054523863</v>
+        <v>0.2219411106615087</v>
       </c>
       <c r="T63">
-        <v>2.240544115178751</v>
+        <v>2.295709150022245</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.084901713802097</v>
+        <v>2.051274266805288</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1242842220513733</v>
+        <v>0.1243598269763159</v>
       </c>
       <c r="C64">
-        <v>286.7444390808674</v>
+        <v>277.8944053061804</v>
       </c>
       <c r="D64">
-        <v>776.2304390808674</v>
+        <v>775.4834053061804</v>
       </c>
       <c r="E64">
-        <v>246.186</v>
+        <v>254.289</v>
       </c>
       <c r="F64">
-        <v>502.386</v>
+        <v>510.489</v>
       </c>
       <c r="G64">
         <v>12.9</v>
@@ -6523,28 +6523,28 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M64">
-        <v>38.0808588</v>
+        <v>38.6950662</v>
       </c>
       <c r="N64">
-        <v>40.03342691428573</v>
+        <v>39.41921951428573</v>
       </c>
       <c r="O64">
-        <v>6.005014037142859</v>
+        <v>5.912882927142859</v>
       </c>
       <c r="P64">
-        <v>34.02841287714287</v>
+        <v>33.50633658714287</v>
       </c>
       <c r="Q64">
-        <v>86.62841287714286</v>
+        <v>86.10633658714286</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2219411106615087</v>
+        <v>0.2264025053413943</v>
       </c>
       <c r="T64">
-        <v>2.295709150022245</v>
+        <v>2.353856078641062</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.051274266805288</v>
+        <v>2.018714357808379</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1243598269763159</v>
+        <v>0.1321602319012585</v>
       </c>
       <c r="C65">
-        <v>277.8944053061804</v>
+        <v>199.7466122250559</v>
       </c>
       <c r="D65">
-        <v>775.4834053061804</v>
+        <v>705.4386122250559</v>
       </c>
       <c r="E65">
-        <v>254.289</v>
+        <v>262.392</v>
       </c>
       <c r="F65">
-        <v>510.489</v>
+        <v>518.592</v>
       </c>
       <c r="G65">
         <v>12.9</v>
@@ -6605,45 +6605,45 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M65">
-        <v>38.6950662</v>
+        <v>46.67328</v>
       </c>
       <c r="N65">
-        <v>39.41921951428573</v>
+        <v>31.44100571428573</v>
       </c>
       <c r="O65">
-        <v>5.912882927142859</v>
+        <v>4.71615085714286</v>
       </c>
       <c r="P65">
-        <v>33.50633658714287</v>
+        <v>26.72485485714287</v>
       </c>
       <c r="Q65">
-        <v>86.10633658714286</v>
+        <v>79.32485485714287</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2264025053413943</v>
+        <v>0.2311117552812736</v>
       </c>
       <c r="T65">
-        <v>2.353856078641062</v>
+        <v>2.415233392183148</v>
       </c>
       <c r="U65">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V65">
         <v>0.15</v>
       </c>
       <c r="W65">
-        <v>0.06443</v>
+        <v>0.0765</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y65">
-        <v>2.018714357808379</v>
+        <v>1.67364037227051</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1321602319012585</v>
+        <v>0.1323565368262011</v>
       </c>
       <c r="C66">
-        <v>199.7466122250559</v>
+        <v>190.0437206524236</v>
       </c>
       <c r="D66">
-        <v>705.4386122250559</v>
+        <v>703.8387206524236</v>
       </c>
       <c r="E66">
-        <v>262.392</v>
+        <v>270.4949999999999</v>
       </c>
       <c r="F66">
-        <v>518.592</v>
+        <v>526.6949999999999</v>
       </c>
       <c r="G66">
         <v>12.9</v>
@@ -6687,28 +6687,28 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M66">
-        <v>46.67328</v>
+        <v>47.40254999999999</v>
       </c>
       <c r="N66">
-        <v>31.44100571428573</v>
+        <v>30.71173571428574</v>
       </c>
       <c r="O66">
-        <v>4.71615085714286</v>
+        <v>4.606760357142861</v>
       </c>
       <c r="P66">
-        <v>26.72485485714287</v>
+        <v>26.10497535714288</v>
       </c>
       <c r="Q66">
-        <v>79.32485485714287</v>
+        <v>78.70497535714287</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2311117552812736</v>
+        <v>0.2360901052177174</v>
       </c>
       <c r="T66">
-        <v>2.415233392183148</v>
+        <v>2.480117980784782</v>
       </c>
       <c r="U66">
         <v>0.09</v>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>1.67364037227051</v>
+        <v>1.647892058850964</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1323565368262011</v>
+        <v>0.1325528417511437</v>
       </c>
       <c r="C67">
-        <v>190.0437206524236</v>
+        <v>180.3480695710251</v>
       </c>
       <c r="D67">
-        <v>703.8387206524236</v>
+        <v>702.2460695710251</v>
       </c>
       <c r="E67">
-        <v>270.4949999999999</v>
+        <v>278.598</v>
       </c>
       <c r="F67">
-        <v>526.6949999999999</v>
+        <v>534.798</v>
       </c>
       <c r="G67">
         <v>12.9</v>
@@ -6769,28 +6769,28 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M67">
-        <v>47.40254999999999</v>
+        <v>48.13182</v>
       </c>
       <c r="N67">
-        <v>30.71173571428574</v>
+        <v>29.98246571428573</v>
       </c>
       <c r="O67">
-        <v>4.606760357142861</v>
+        <v>4.49736985714286</v>
       </c>
       <c r="P67">
-        <v>26.10497535714288</v>
+        <v>25.48509585714287</v>
       </c>
       <c r="Q67">
-        <v>78.70497535714287</v>
+        <v>78.08509585714286</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2360901052177174</v>
+        <v>0.2413612992680697</v>
       </c>
       <c r="T67">
-        <v>2.480117980784782</v>
+        <v>2.548819309892393</v>
       </c>
       <c r="U67">
         <v>0.09</v>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>1.647892058850964</v>
+        <v>1.622923997353221</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1325528417511437</v>
+        <v>0.1327491466760863</v>
       </c>
       <c r="C68">
-        <v>180.3480695710251</v>
+        <v>170.6596099403295</v>
       </c>
       <c r="D68">
-        <v>702.2460695710251</v>
+        <v>700.6606099403294</v>
       </c>
       <c r="E68">
-        <v>278.598</v>
+        <v>286.701</v>
       </c>
       <c r="F68">
-        <v>534.798</v>
+        <v>542.901</v>
       </c>
       <c r="G68">
         <v>12.9</v>
@@ -6851,28 +6851,28 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M68">
-        <v>48.13182</v>
+        <v>48.86109</v>
       </c>
       <c r="N68">
-        <v>29.98246571428573</v>
+        <v>29.25319571428573</v>
       </c>
       <c r="O68">
-        <v>4.49736985714286</v>
+        <v>4.38797935714286</v>
       </c>
       <c r="P68">
-        <v>25.48509585714287</v>
+        <v>24.86521635714287</v>
       </c>
       <c r="Q68">
-        <v>78.08509585714286</v>
+        <v>77.46521635714286</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2413612992680697</v>
+        <v>0.2469519596245039</v>
       </c>
       <c r="T68">
-        <v>2.548819309892393</v>
+        <v>2.621684355915618</v>
       </c>
       <c r="U68">
         <v>0.09</v>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>1.622923997353221</v>
+        <v>1.598701251124069</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1327491466760863</v>
+        <v>0.1329454516010289</v>
       </c>
       <c r="C69">
-        <v>170.6596099403295</v>
+        <v>160.9782931616834</v>
       </c>
       <c r="D69">
-        <v>700.6606099403294</v>
+        <v>699.0822931616834</v>
       </c>
       <c r="E69">
-        <v>286.701</v>
+        <v>294.804</v>
       </c>
       <c r="F69">
-        <v>542.901</v>
+        <v>551.004</v>
       </c>
       <c r="G69">
         <v>12.9</v>
@@ -6933,28 +6933,28 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M69">
-        <v>48.86109</v>
+        <v>49.59036</v>
       </c>
       <c r="N69">
-        <v>29.25319571428573</v>
+        <v>28.52392571428573</v>
       </c>
       <c r="O69">
-        <v>4.38797935714286</v>
+        <v>4.27858885714286</v>
       </c>
       <c r="P69">
-        <v>24.86521635714287</v>
+        <v>24.24533685714287</v>
       </c>
       <c r="Q69">
-        <v>77.46521635714286</v>
+        <v>76.84533685714287</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2469519596245039</v>
+        <v>0.2528920362532153</v>
       </c>
       <c r="T69">
-        <v>2.621684355915618</v>
+        <v>2.699103467315294</v>
       </c>
       <c r="U69">
         <v>0.09</v>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>1.598701251124069</v>
+        <v>1.575190938607538</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1329454516010289</v>
+        <v>0.1331417565259715</v>
       </c>
       <c r="C70">
-        <v>160.9782931616834</v>
+        <v>151.3040710733458</v>
       </c>
       <c r="D70">
-        <v>699.0822931616834</v>
+        <v>697.5110710733458</v>
       </c>
       <c r="E70">
-        <v>294.804</v>
+        <v>302.907</v>
       </c>
       <c r="F70">
-        <v>551.004</v>
+        <v>559.107</v>
       </c>
       <c r="G70">
         <v>12.9</v>
@@ -7015,28 +7015,28 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M70">
-        <v>49.59036</v>
+        <v>50.31963</v>
       </c>
       <c r="N70">
-        <v>28.52392571428573</v>
+        <v>27.79465571428573</v>
       </c>
       <c r="O70">
-        <v>4.27858885714286</v>
+        <v>4.16919835714286</v>
       </c>
       <c r="P70">
-        <v>24.24533685714287</v>
+        <v>23.62545735714287</v>
       </c>
       <c r="Q70">
-        <v>76.84533685714287</v>
+        <v>76.22545735714286</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2528920362532153</v>
+        <v>0.2592153436321662</v>
       </c>
       <c r="T70">
-        <v>2.699103467315294</v>
+        <v>2.781517360095595</v>
       </c>
       <c r="U70">
         <v>0.09</v>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>1.575190938607538</v>
+        <v>1.55236208442482</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1331417565259715</v>
+        <v>0.1333380614509141</v>
       </c>
       <c r="C71">
-        <v>151.3040710733458</v>
+        <v>141.6368959455875</v>
       </c>
       <c r="D71">
-        <v>697.5110710733458</v>
+        <v>695.9468959455876</v>
       </c>
       <c r="E71">
-        <v>302.907</v>
+        <v>311.01</v>
       </c>
       <c r="F71">
-        <v>559.107</v>
+        <v>567.21</v>
       </c>
       <c r="G71">
         <v>12.9</v>
@@ -7097,28 +7097,28 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M71">
-        <v>50.31963</v>
+        <v>51.0489</v>
       </c>
       <c r="N71">
-        <v>27.79465571428573</v>
+        <v>27.06538571428572</v>
       </c>
       <c r="O71">
-        <v>4.16919835714286</v>
+        <v>4.059807857142858</v>
       </c>
       <c r="P71">
-        <v>23.62545735714287</v>
+        <v>23.00557785714287</v>
       </c>
       <c r="Q71">
-        <v>76.22545735714286</v>
+        <v>75.60557785714286</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2592153436321662</v>
+        <v>0.2659602048363804</v>
       </c>
       <c r="T71">
-        <v>2.781517360095595</v>
+        <v>2.869425512394582</v>
       </c>
       <c r="U71">
         <v>0.09</v>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>1.55236208442482</v>
+        <v>1.530185483218752</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1333380614509141</v>
+        <v>0.1335343663758567</v>
       </c>
       <c r="C72">
-        <v>141.6368959455875</v>
+        <v>131.9767204758595</v>
       </c>
       <c r="D72">
-        <v>695.9468959455876</v>
+        <v>694.3897204758595</v>
       </c>
       <c r="E72">
-        <v>311.01</v>
+        <v>319.113</v>
       </c>
       <c r="F72">
-        <v>567.21</v>
+        <v>575.313</v>
       </c>
       <c r="G72">
         <v>12.9</v>
@@ -7179,28 +7179,28 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M72">
-        <v>51.0489</v>
+        <v>51.77817</v>
       </c>
       <c r="N72">
-        <v>27.06538571428572</v>
+        <v>26.33611571428573</v>
       </c>
       <c r="O72">
-        <v>4.059807857142858</v>
+        <v>3.95041735714286</v>
       </c>
       <c r="P72">
-        <v>23.00557785714287</v>
+        <v>22.38569835714287</v>
       </c>
       <c r="Q72">
-        <v>75.60557785714286</v>
+        <v>74.98569835714287</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2659602048363804</v>
+        <v>0.2731702288822646</v>
       </c>
       <c r="T72">
-        <v>2.869425512394582</v>
+        <v>2.963396295886603</v>
       </c>
       <c r="U72">
         <v>0.09</v>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>1.530185483218752</v>
+        <v>1.508633575004403</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1335343663758567</v>
+        <v>0.1705872596611657</v>
       </c>
       <c r="C73">
-        <v>131.9767204758592</v>
+        <v>-82.31037460780396</v>
       </c>
       <c r="D73">
-        <v>694.3897204758592</v>
+        <v>488.205625392196</v>
       </c>
       <c r="E73">
-        <v>319.113</v>
+        <v>327.216</v>
       </c>
       <c r="F73">
-        <v>575.313</v>
+        <v>583.4159999999999</v>
       </c>
       <c r="G73">
         <v>12.9</v>
@@ -7261,45 +7261,45 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M73">
-        <v>51.77817</v>
+        <v>85.6454688</v>
       </c>
       <c r="N73">
-        <v>26.33611571428573</v>
+        <v>-7.531183085714275</v>
       </c>
       <c r="O73">
-        <v>3.95041735714286</v>
+        <v>-1.129677462857141</v>
       </c>
       <c r="P73">
-        <v>22.38569835714287</v>
+        <v>-6.401505622857134</v>
       </c>
       <c r="Q73">
-        <v>74.98569835714287</v>
+        <v>46.19849437714286</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2731702288822645</v>
+        <v>0.2833982588485105</v>
       </c>
       <c r="T73">
-        <v>2.963396295886601</v>
+        <v>3.096701813786596</v>
       </c>
       <c r="U73">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V73">
-        <v>0.15</v>
+        <v>0.136809839695137</v>
       </c>
       <c r="W73">
-        <v>0.0765</v>
+        <v>0.1267163155327539</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y73">
-        <v>1.508633575004403</v>
+        <v>0.9120655979675801</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1705872596611657</v>
+        <v>0.1715972596611657</v>
       </c>
       <c r="C74">
-        <v>-82.31037460780396</v>
+        <v>-94.33307590316008</v>
       </c>
       <c r="D74">
-        <v>488.205625392196</v>
+        <v>484.2859240968399</v>
       </c>
       <c r="E74">
-        <v>327.216</v>
+        <v>335.319</v>
       </c>
       <c r="F74">
-        <v>583.4159999999999</v>
+        <v>591.519</v>
       </c>
       <c r="G74">
         <v>12.9</v>
@@ -7343,37 +7343,37 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M74">
-        <v>85.6454688</v>
+        <v>86.83498920000001</v>
       </c>
       <c r="N74">
-        <v>-7.531183085714275</v>
+        <v>-8.720703485714282</v>
       </c>
       <c r="O74">
-        <v>-1.129677462857141</v>
+        <v>-1.308105522857142</v>
       </c>
       <c r="P74">
-        <v>-6.401505622857134</v>
+        <v>-7.41259796285714</v>
       </c>
       <c r="Q74">
-        <v>46.19849437714286</v>
+        <v>45.18740203714285</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2833982588485105</v>
+        <v>0.2921981943614183</v>
       </c>
       <c r="T74">
-        <v>3.096701813786596</v>
+        <v>3.21139447355647</v>
       </c>
       <c r="U74">
         <v>0.1468</v>
       </c>
       <c r="V74">
-        <v>0.136809839695137</v>
+        <v>0.1349357323020529</v>
       </c>
       <c r="W74">
-        <v>0.1267163155327539</v>
+        <v>0.1269914344980586</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.9120655979675801</v>
+        <v>0.8995715486803529</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1715972596611657</v>
+        <v>0.1726072596611657</v>
       </c>
       <c r="C75">
-        <v>-94.33307590316008</v>
+        <v>-106.2933375823792</v>
       </c>
       <c r="D75">
-        <v>484.2859240968399</v>
+        <v>480.4286624176208</v>
       </c>
       <c r="E75">
-        <v>335.319</v>
+        <v>343.422</v>
       </c>
       <c r="F75">
-        <v>591.519</v>
+        <v>599.622</v>
       </c>
       <c r="G75">
         <v>12.9</v>
@@ -7425,37 +7425,37 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M75">
-        <v>86.83498920000001</v>
+        <v>88.0245096</v>
       </c>
       <c r="N75">
-        <v>-8.720703485714282</v>
+        <v>-9.910223885714274</v>
       </c>
       <c r="O75">
-        <v>-1.308105522857142</v>
+        <v>-1.486533582857141</v>
       </c>
       <c r="P75">
-        <v>-7.41259796285714</v>
+        <v>-8.423690302857132</v>
       </c>
       <c r="Q75">
-        <v>45.18740203714285</v>
+        <v>44.17630969714286</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2921981943614183</v>
+        <v>0.3016750479907036</v>
       </c>
       <c r="T75">
-        <v>3.21139447355647</v>
+        <v>3.334909645616334</v>
       </c>
       <c r="U75">
         <v>0.1468</v>
       </c>
       <c r="V75">
-        <v>0.1349357323020529</v>
+        <v>0.1331122764601333</v>
       </c>
       <c r="W75">
-        <v>0.1269914344980586</v>
+        <v>0.1272591178156524</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.8995715486803529</v>
+        <v>0.8874151764008887</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1726072596611657</v>
+        <v>0.1736172596611658</v>
       </c>
       <c r="C76">
-        <v>-106.2933375823792</v>
+        <v>-118.1926398214361</v>
       </c>
       <c r="D76">
-        <v>480.4286624176208</v>
+        <v>476.6323601785638</v>
       </c>
       <c r="E76">
-        <v>343.422</v>
+        <v>351.5249999999999</v>
       </c>
       <c r="F76">
-        <v>599.622</v>
+        <v>607.7249999999999</v>
       </c>
       <c r="G76">
         <v>12.9</v>
@@ -7507,37 +7507,37 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M76">
-        <v>88.0245096</v>
+        <v>89.21402999999999</v>
       </c>
       <c r="N76">
-        <v>-9.910223885714274</v>
+        <v>-11.09974428571427</v>
       </c>
       <c r="O76">
-        <v>-1.486533582857141</v>
+        <v>-1.66496164285714</v>
       </c>
       <c r="P76">
-        <v>-8.423690302857132</v>
+        <v>-9.434782642857126</v>
       </c>
       <c r="Q76">
-        <v>44.17630969714286</v>
+        <v>43.16521735714286</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3016750479907036</v>
+        <v>0.3119100499103318</v>
       </c>
       <c r="T76">
-        <v>3.334909645616334</v>
+        <v>3.468306031440988</v>
       </c>
       <c r="U76">
         <v>0.1468</v>
       </c>
       <c r="V76">
-        <v>0.1331122764601333</v>
+        <v>0.1313374461073315</v>
       </c>
       <c r="W76">
-        <v>0.1272591178156524</v>
+        <v>0.1275196629114437</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.8874151764008887</v>
+        <v>0.875582974048877</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1736172596611658</v>
+        <v>0.1746272596611657</v>
       </c>
       <c r="C77">
-        <v>-118.1926398214361</v>
+        <v>-130.0324163782495</v>
       </c>
       <c r="D77">
-        <v>476.6323601785638</v>
+        <v>472.8955836217505</v>
       </c>
       <c r="E77">
-        <v>351.5249999999999</v>
+        <v>359.628</v>
       </c>
       <c r="F77">
-        <v>607.7249999999999</v>
+        <v>615.828</v>
       </c>
       <c r="G77">
         <v>12.9</v>
@@ -7589,37 +7589,37 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M77">
-        <v>89.21402999999999</v>
+        <v>90.4035504</v>
       </c>
       <c r="N77">
-        <v>-11.09974428571427</v>
+        <v>-12.28926468571427</v>
       </c>
       <c r="O77">
-        <v>-1.66496164285714</v>
+        <v>-1.843389702857141</v>
       </c>
       <c r="P77">
-        <v>-9.434782642857126</v>
+        <v>-10.44587498285713</v>
       </c>
       <c r="Q77">
-        <v>43.16521735714286</v>
+        <v>42.15412501714286</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3119100499103318</v>
+        <v>0.3229979686565956</v>
       </c>
       <c r="T77">
-        <v>3.468306031440988</v>
+        <v>3.612818782751029</v>
       </c>
       <c r="U77">
         <v>0.1468</v>
       </c>
       <c r="V77">
-        <v>0.1313374461073315</v>
+        <v>0.1296093218164456</v>
       </c>
       <c r="W77">
-        <v>0.1275196629114437</v>
+        <v>0.1277733515573458</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.875582974048877</v>
+        <v>0.8640621454429707</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1746272596611657</v>
+        <v>0.1756372596611658</v>
       </c>
       <c r="C78">
-        <v>-130.0324163782495</v>
+        <v>-141.8140563981053</v>
       </c>
       <c r="D78">
-        <v>472.8955836217505</v>
+        <v>469.2169436018946</v>
       </c>
       <c r="E78">
-        <v>359.628</v>
+        <v>367.7309999999999</v>
       </c>
       <c r="F78">
-        <v>615.828</v>
+        <v>623.9309999999999</v>
       </c>
       <c r="G78">
         <v>12.9</v>
@@ -7671,37 +7671,37 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M78">
-        <v>90.4035504</v>
+        <v>91.59307079999999</v>
       </c>
       <c r="N78">
-        <v>-12.28926468571427</v>
+        <v>-13.47878508571426</v>
       </c>
       <c r="O78">
-        <v>-1.843389702857141</v>
+        <v>-2.02181776285714</v>
       </c>
       <c r="P78">
-        <v>-10.44587498285713</v>
+        <v>-11.45696732285712</v>
       </c>
       <c r="Q78">
-        <v>42.15412501714286</v>
+        <v>41.14303267714287</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3229979686565956</v>
+        <v>0.3350500542503607</v>
       </c>
       <c r="T78">
-        <v>3.612818782751029</v>
+        <v>3.769897860261944</v>
       </c>
       <c r="U78">
         <v>0.1468</v>
       </c>
       <c r="V78">
-        <v>0.1296093218164456</v>
+        <v>0.1279260838707775</v>
       </c>
       <c r="W78">
-        <v>0.1277733515573458</v>
+        <v>0.1280204508877699</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.8640621454429707</v>
+        <v>0.8528405591385165</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1756372596611658</v>
+        <v>0.1766472596611658</v>
       </c>
       <c r="C79">
-        <v>-141.8140563981053</v>
+        <v>-153.5389061354641</v>
       </c>
       <c r="D79">
-        <v>469.2169436018946</v>
+        <v>465.595093864536</v>
       </c>
       <c r="E79">
-        <v>367.7309999999999</v>
+        <v>375.834</v>
       </c>
       <c r="F79">
-        <v>623.9309999999999</v>
+        <v>632.034</v>
       </c>
       <c r="G79">
         <v>12.9</v>
@@ -7753,37 +7753,37 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M79">
-        <v>91.59307079999999</v>
+        <v>92.78259120000001</v>
       </c>
       <c r="N79">
-        <v>-13.47878508571426</v>
+        <v>-14.66830548571428</v>
       </c>
       <c r="O79">
-        <v>-2.02181776285714</v>
+        <v>-2.200245822857143</v>
       </c>
       <c r="P79">
-        <v>-11.45696732285712</v>
+        <v>-12.46805966285714</v>
       </c>
       <c r="Q79">
-        <v>41.14303267714287</v>
+        <v>40.13194033714285</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3350500542503607</v>
+        <v>0.3481977839890135</v>
       </c>
       <c r="T79">
-        <v>3.769897860261944</v>
+        <v>3.941256853910214</v>
       </c>
       <c r="U79">
         <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.1279260838707775</v>
+        <v>0.1262860058724342</v>
       </c>
       <c r="W79">
-        <v>0.1280204508877699</v>
+        <v>0.1282612143379267</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.8528405591385165</v>
+        <v>0.8419067058162277</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1766472596611658</v>
+        <v>0.1776572596611657</v>
       </c>
       <c r="C80">
-        <v>-153.5389061354641</v>
+        <v>-165.2082705966365</v>
       </c>
       <c r="D80">
-        <v>465.595093864536</v>
+        <v>462.0287294033635</v>
       </c>
       <c r="E80">
-        <v>375.834</v>
+        <v>383.937</v>
       </c>
       <c r="F80">
-        <v>632.034</v>
+        <v>640.1369999999999</v>
       </c>
       <c r="G80">
         <v>12.9</v>
@@ -7835,37 +7835,37 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M80">
-        <v>92.78259120000001</v>
+        <v>93.97211160000001</v>
       </c>
       <c r="N80">
-        <v>-14.66830548571428</v>
+        <v>-15.85782588571428</v>
       </c>
       <c r="O80">
-        <v>-2.200245822857143</v>
+        <v>-2.378673882857142</v>
       </c>
       <c r="P80">
-        <v>-12.46805966285714</v>
+        <v>-13.47915200285714</v>
       </c>
       <c r="Q80">
-        <v>40.13194033714285</v>
+        <v>39.12084799714286</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3481977839890135</v>
+        <v>0.3625976784646808</v>
       </c>
       <c r="T80">
-        <v>3.941256853910214</v>
+        <v>4.128935751715463</v>
       </c>
       <c r="U80">
         <v>0.1468</v>
       </c>
       <c r="V80">
-        <v>0.1262860058724342</v>
+        <v>0.1246874488360742</v>
       </c>
       <c r="W80">
-        <v>0.1282612143379267</v>
+        <v>0.1284958825108643</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.8419067058162277</v>
+        <v>0.8312496589071616</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1776572596611657</v>
+        <v>0.1786672596611658</v>
       </c>
       <c r="C81">
-        <v>-165.2082705966365</v>
+        <v>-176.8234151075375</v>
       </c>
       <c r="D81">
-        <v>462.0287294033635</v>
+        <v>458.5165848924625</v>
       </c>
       <c r="E81">
-        <v>383.937</v>
+        <v>392.04</v>
       </c>
       <c r="F81">
-        <v>640.1369999999999</v>
+        <v>648.24</v>
       </c>
       <c r="G81">
         <v>12.9</v>
@@ -7917,37 +7917,37 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M81">
-        <v>93.97211160000001</v>
+        <v>95.16163200000001</v>
       </c>
       <c r="N81">
-        <v>-15.85782588571428</v>
+        <v>-17.04734628571428</v>
       </c>
       <c r="O81">
-        <v>-2.378673882857142</v>
+        <v>-2.557101942857142</v>
       </c>
       <c r="P81">
-        <v>-13.47915200285714</v>
+        <v>-14.49024434285714</v>
       </c>
       <c r="Q81">
-        <v>39.12084799714286</v>
+        <v>38.10975565714286</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3625976784646808</v>
+        <v>0.3784375623879148</v>
       </c>
       <c r="T81">
-        <v>4.128935751715463</v>
+        <v>4.335382539301236</v>
       </c>
       <c r="U81">
         <v>0.1468</v>
       </c>
       <c r="V81">
-        <v>0.1246874488360742</v>
+        <v>0.1231288557256233</v>
       </c>
       <c r="W81">
-        <v>0.1284958825108643</v>
+        <v>0.1287246839794785</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.8312496589071616</v>
+        <v>0.8208590381708221</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1786672596611658</v>
+        <v>0.1796772596611658</v>
       </c>
       <c r="C82">
-        <v>-176.8234151075375</v>
+        <v>-188.3855668104738</v>
       </c>
       <c r="D82">
-        <v>458.5165848924625</v>
+        <v>455.0574331895261</v>
       </c>
       <c r="E82">
-        <v>392.04</v>
+        <v>400.143</v>
       </c>
       <c r="F82">
-        <v>648.24</v>
+        <v>656.343</v>
       </c>
       <c r="G82">
         <v>12.9</v>
@@ -7999,37 +7999,37 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M82">
-        <v>95.16163200000001</v>
+        <v>96.3511524</v>
       </c>
       <c r="N82">
-        <v>-17.04734628571428</v>
+        <v>-18.23686668571428</v>
       </c>
       <c r="O82">
-        <v>-2.557101942857142</v>
+        <v>-2.735530002857141</v>
       </c>
       <c r="P82">
-        <v>-14.49024434285714</v>
+        <v>-15.50133668285713</v>
       </c>
       <c r="Q82">
-        <v>38.10975565714286</v>
+        <v>37.09866331714286</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3784375623879148</v>
+        <v>0.3959448025135945</v>
       </c>
       <c r="T82">
-        <v>4.335382539301236</v>
+        <v>4.563560567685512</v>
       </c>
       <c r="U82">
         <v>0.1468</v>
       </c>
       <c r="V82">
-        <v>0.1231288557256233</v>
+        <v>0.1216087463956773</v>
       </c>
       <c r="W82">
-        <v>0.1287246839794785</v>
+        <v>0.1289478360291146</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.8208590381708221</v>
+        <v>0.8107249759711823</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1796772596611658</v>
+        <v>0.1806872596611657</v>
       </c>
       <c r="C83">
-        <v>-188.3855668104738</v>
+        <v>-199.8959160936898</v>
       </c>
       <c r="D83">
-        <v>455.0574331895261</v>
+        <v>451.6500839063103</v>
       </c>
       <c r="E83">
-        <v>400.143</v>
+        <v>408.246</v>
       </c>
       <c r="F83">
-        <v>656.343</v>
+        <v>664.446</v>
       </c>
       <c r="G83">
         <v>12.9</v>
@@ -8081,37 +8081,37 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M83">
-        <v>96.3511524</v>
+        <v>97.54067280000001</v>
       </c>
       <c r="N83">
-        <v>-18.23686668571428</v>
+        <v>-19.42638708571428</v>
       </c>
       <c r="O83">
-        <v>-2.735530002857141</v>
+        <v>-2.913958062857142</v>
       </c>
       <c r="P83">
-        <v>-15.50133668285713</v>
+        <v>-16.51242902285714</v>
       </c>
       <c r="Q83">
-        <v>37.09866331714286</v>
+        <v>36.08757097714285</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3959448025135945</v>
+        <v>0.4153972915421276</v>
       </c>
       <c r="T83">
-        <v>4.563560567685512</v>
+        <v>4.817091710334707</v>
       </c>
       <c r="U83">
         <v>0.1468</v>
       </c>
       <c r="V83">
-        <v>0.1216087463956773</v>
+        <v>0.1201257129030471</v>
       </c>
       <c r="W83">
-        <v>0.1289478360291146</v>
+        <v>0.1291655453458327</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.8107249759711823</v>
+        <v>0.8008380860203141</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1806872596611657</v>
+        <v>0.2284721253398353</v>
       </c>
       <c r="C84">
-        <v>-199.8959160936898</v>
+        <v>-326.1452318113866</v>
       </c>
       <c r="D84">
-        <v>451.6500839063103</v>
+        <v>333.5037681886134</v>
       </c>
       <c r="E84">
-        <v>408.246</v>
+        <v>416.349</v>
       </c>
       <c r="F84">
-        <v>664.446</v>
+        <v>672.549</v>
       </c>
       <c r="G84">
         <v>12.9</v>
@@ -8163,45 +8163,45 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M84">
-        <v>97.54067280000001</v>
+        <v>135.0478392</v>
       </c>
       <c r="N84">
-        <v>-19.42638708571428</v>
+        <v>-56.93355348571427</v>
       </c>
       <c r="O84">
-        <v>-2.913958062857142</v>
+        <v>-8.540033022857139</v>
       </c>
       <c r="P84">
-        <v>-16.51242902285714</v>
+        <v>-48.39352046285713</v>
       </c>
       <c r="Q84">
-        <v>36.08757097714285</v>
+        <v>4.206479537142862</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4153972915421276</v>
+        <v>0.4486375185661913</v>
       </c>
       <c r="T84">
-        <v>4.817091710334707</v>
+        <v>5.250323299719907</v>
       </c>
       <c r="U84">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.1201257129030471</v>
+        <v>0.0867629051049849</v>
       </c>
       <c r="W84">
-        <v>0.1291655453458327</v>
+        <v>0.183378008654919</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y84">
-        <v>0.8008380860203141</v>
+        <v>0.578419367366566</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2284721253398353</v>
+        <v>0.2300221253398353</v>
       </c>
       <c r="C85">
-        <v>-326.1452318113866</v>
+        <v>-337.0542511195385</v>
       </c>
       <c r="D85">
-        <v>333.5037681886134</v>
+        <v>330.6977488804615</v>
       </c>
       <c r="E85">
-        <v>416.349</v>
+        <v>424.4520000000001</v>
       </c>
       <c r="F85">
-        <v>672.549</v>
+        <v>680.652</v>
       </c>
       <c r="G85">
         <v>12.9</v>
@@ -8245,37 +8245,37 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M85">
-        <v>135.0478392</v>
+        <v>136.6749216</v>
       </c>
       <c r="N85">
-        <v>-56.93355348571427</v>
+        <v>-58.56063588571428</v>
       </c>
       <c r="O85">
-        <v>-8.540033022857139</v>
+        <v>-8.78409538285714</v>
       </c>
       <c r="P85">
-        <v>-48.39352046285713</v>
+        <v>-49.77654050285714</v>
       </c>
       <c r="Q85">
-        <v>4.206479537142862</v>
+        <v>2.823459497142856</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4486375185661913</v>
+        <v>0.4738148634765784</v>
       </c>
       <c r="T85">
-        <v>5.250323299719907</v>
+        <v>5.578468505952403</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.0867629051049849</v>
+        <v>0.08573001337754459</v>
       </c>
       <c r="W85">
-        <v>0.183378008654919</v>
+        <v>0.1835854133137891</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.578419367366566</v>
+        <v>0.5715334225169639</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2300221253398353</v>
+        <v>0.2315721253398353</v>
       </c>
       <c r="C86">
-        <v>-337.0542511195384</v>
+        <v>-347.9164460731787</v>
       </c>
       <c r="D86">
-        <v>330.6977488804615</v>
+        <v>327.9385539268213</v>
       </c>
       <c r="E86">
-        <v>424.4519999999999</v>
+        <v>432.555</v>
       </c>
       <c r="F86">
-        <v>680.6519999999999</v>
+        <v>688.755</v>
       </c>
       <c r="G86">
         <v>12.9</v>
@@ -8327,37 +8327,37 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M86">
-        <v>136.6749216</v>
+        <v>138.302004</v>
       </c>
       <c r="N86">
-        <v>-58.56063588571425</v>
+        <v>-60.18771828571428</v>
       </c>
       <c r="O86">
-        <v>-8.784095382857137</v>
+        <v>-9.028157742857141</v>
       </c>
       <c r="P86">
-        <v>-49.77654050285711</v>
+        <v>-51.15956054285714</v>
       </c>
       <c r="Q86">
-        <v>2.823459497142885</v>
+        <v>1.440439457142851</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4738148634765781</v>
+        <v>0.50234918770835</v>
       </c>
       <c r="T86">
-        <v>5.578468505952399</v>
+        <v>5.950366406349226</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.0857300133775446</v>
+        <v>0.08472142498486759</v>
       </c>
       <c r="W86">
-        <v>0.1835854133137891</v>
+        <v>0.1837879378630386</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.5715334225169642</v>
+        <v>0.5648094998991173</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2315721253398353</v>
+        <v>0.2331221253398353</v>
       </c>
       <c r="C87">
-        <v>-347.9164460731787</v>
+        <v>-358.732979018977</v>
       </c>
       <c r="D87">
-        <v>327.9385539268213</v>
+        <v>325.225020981023</v>
       </c>
       <c r="E87">
-        <v>432.555</v>
+        <v>440.658</v>
       </c>
       <c r="F87">
-        <v>688.755</v>
+        <v>696.8579999999999</v>
       </c>
       <c r="G87">
         <v>12.9</v>
@@ -8409,37 +8409,37 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M87">
-        <v>138.302004</v>
+        <v>139.9290864</v>
       </c>
       <c r="N87">
-        <v>-60.18771828571428</v>
+        <v>-61.81480068571426</v>
       </c>
       <c r="O87">
-        <v>-9.028157742857141</v>
+        <v>-9.272220102857139</v>
       </c>
       <c r="P87">
-        <v>-51.15956054285714</v>
+        <v>-52.54258058285712</v>
       </c>
       <c r="Q87">
-        <v>1.440439457142851</v>
+        <v>0.05741941714287435</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.50234918770835</v>
+        <v>0.5349598439732322</v>
       </c>
       <c r="T87">
-        <v>5.950366406349226</v>
+        <v>6.375392578231313</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.08472142498486759</v>
+        <v>0.08373629213620636</v>
       </c>
       <c r="W87">
-        <v>0.1837879378630386</v>
+        <v>0.1839857525390498</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.5648094998991173</v>
+        <v>0.5582419475747091</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2331221253398353</v>
+        <v>0.2346721253398353</v>
       </c>
       <c r="C88">
-        <v>-358.732979018977</v>
+        <v>-369.504974147896</v>
       </c>
       <c r="D88">
-        <v>325.225020981023</v>
+        <v>322.5560258521041</v>
       </c>
       <c r="E88">
-        <v>440.658</v>
+        <v>448.761</v>
       </c>
       <c r="F88">
-        <v>696.8579999999999</v>
+        <v>704.961</v>
       </c>
       <c r="G88">
         <v>12.9</v>
@@ -8491,37 +8491,37 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M88">
-        <v>139.9290864</v>
+        <v>141.5561688</v>
       </c>
       <c r="N88">
-        <v>-61.81480068571426</v>
+        <v>-63.44188308571427</v>
       </c>
       <c r="O88">
-        <v>-9.272220102857139</v>
+        <v>-9.51628246285714</v>
       </c>
       <c r="P88">
-        <v>-52.54258058285712</v>
+        <v>-53.92560062285713</v>
       </c>
       <c r="Q88">
-        <v>0.05741941714287435</v>
+        <v>-1.325600622857131</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.5349598439732322</v>
+        <v>0.5725875242788654</v>
       </c>
       <c r="T88">
-        <v>6.375392578231313</v>
+        <v>6.865807391941415</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.08373629213620636</v>
+        <v>0.08277380601969823</v>
       </c>
       <c r="W88">
-        <v>0.1839857525390498</v>
+        <v>0.1841790197512446</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.5582419475747091</v>
+        <v>0.551825373464655</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2346721253398353</v>
+        <v>0.2362221253398353</v>
       </c>
       <c r="C89">
-        <v>-369.504974147896</v>
+        <v>-380.2335190480932</v>
       </c>
       <c r="D89">
-        <v>322.5560258521041</v>
+        <v>319.9304809519068</v>
       </c>
       <c r="E89">
-        <v>448.761</v>
+        <v>456.864</v>
       </c>
       <c r="F89">
-        <v>704.961</v>
+        <v>713.064</v>
       </c>
       <c r="G89">
         <v>12.9</v>
@@ -8573,37 +8573,37 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M89">
-        <v>141.5561688</v>
+        <v>143.1832512</v>
       </c>
       <c r="N89">
-        <v>-63.44188308571427</v>
+        <v>-65.06896548571427</v>
       </c>
       <c r="O89">
-        <v>-9.51628246285714</v>
+        <v>-9.760344822857141</v>
       </c>
       <c r="P89">
-        <v>-53.92560062285713</v>
+        <v>-55.30862066285713</v>
       </c>
       <c r="Q89">
-        <v>-1.325600622857131</v>
+        <v>-2.708620662857136</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5725875242788654</v>
+        <v>0.6164864846354374</v>
       </c>
       <c r="T89">
-        <v>6.865807391941415</v>
+        <v>7.437958007936532</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.08277380601969823</v>
+        <v>0.0818331945876562</v>
       </c>
       <c r="W89">
-        <v>0.1841790197512446</v>
+        <v>0.1843678945267986</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.551825373464655</v>
+        <v>0.5455546305843747</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2362221253398353</v>
+        <v>0.2377721253398353</v>
       </c>
       <c r="C90">
-        <v>-380.2335190480932</v>
+        <v>-390.9196661825931</v>
       </c>
       <c r="D90">
-        <v>319.9304809519068</v>
+        <v>317.3473338174068</v>
       </c>
       <c r="E90">
-        <v>456.864</v>
+        <v>464.9669999999999</v>
       </c>
       <c r="F90">
-        <v>713.064</v>
+        <v>721.1669999999999</v>
       </c>
       <c r="G90">
         <v>12.9</v>
@@ -8655,37 +8655,37 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M90">
-        <v>143.1832512</v>
+        <v>144.8103336</v>
       </c>
       <c r="N90">
-        <v>-65.06896548571427</v>
+        <v>-66.69604788571425</v>
       </c>
       <c r="O90">
-        <v>-9.760344822857141</v>
+        <v>-10.00440718285714</v>
       </c>
       <c r="P90">
-        <v>-55.30862066285713</v>
+        <v>-56.69164070285711</v>
       </c>
       <c r="Q90">
-        <v>-2.708620662857136</v>
+        <v>-4.09164070285712</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.6164864846354374</v>
+        <v>0.66836707414775</v>
       </c>
       <c r="T90">
-        <v>7.437958007936532</v>
+        <v>8.114136008658036</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.0818331945876562</v>
+        <v>0.0809137204911657</v>
       </c>
       <c r="W90">
-        <v>0.1843678945267986</v>
+        <v>0.1845525249253739</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5455546305843747</v>
+        <v>0.539424803274438</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2377721253398353</v>
+        <v>0.2393221253398353</v>
       </c>
       <c r="C91">
-        <v>-390.9196661825931</v>
+        <v>-401.5644342959456</v>
       </c>
       <c r="D91">
-        <v>317.3473338174068</v>
+        <v>314.8055657040544</v>
       </c>
       <c r="E91">
-        <v>464.9669999999999</v>
+        <v>473.07</v>
       </c>
       <c r="F91">
-        <v>721.1669999999999</v>
+        <v>729.27</v>
       </c>
       <c r="G91">
         <v>12.9</v>
@@ -8737,37 +8737,37 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M91">
-        <v>144.8103336</v>
+        <v>146.437416</v>
       </c>
       <c r="N91">
-        <v>-66.69604788571425</v>
+        <v>-68.32313028571429</v>
       </c>
       <c r="O91">
-        <v>-10.00440718285714</v>
+        <v>-10.24846954285714</v>
       </c>
       <c r="P91">
-        <v>-56.69164070285711</v>
+        <v>-58.07466074285714</v>
       </c>
       <c r="Q91">
-        <v>-4.09164070285712</v>
+        <v>-5.474660742857147</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.66836707414775</v>
+        <v>0.7306237815625252</v>
       </c>
       <c r="T91">
-        <v>8.114136008658036</v>
+        <v>8.925549609523841</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.0809137204911657</v>
+        <v>0.08001467915237494</v>
       </c>
       <c r="W91">
-        <v>0.1845525249253739</v>
+        <v>0.1847330524262031</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.539424803274438</v>
+        <v>0.5334311943491663</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2393221253398353</v>
+        <v>0.2408721253398353</v>
       </c>
       <c r="C92">
-        <v>-401.5644342959456</v>
+        <v>-412.1688097538242</v>
       </c>
       <c r="D92">
-        <v>314.8055657040544</v>
+        <v>312.3041902461758</v>
       </c>
       <c r="E92">
-        <v>473.07</v>
+        <v>481.1729999999999</v>
       </c>
       <c r="F92">
-        <v>729.27</v>
+        <v>737.3729999999999</v>
       </c>
       <c r="G92">
         <v>12.9</v>
@@ -8819,37 +8819,37 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M92">
-        <v>146.437416</v>
+        <v>148.0644984</v>
       </c>
       <c r="N92">
-        <v>-68.32313028571429</v>
+        <v>-69.95021268571426</v>
       </c>
       <c r="O92">
-        <v>-10.24846954285714</v>
+        <v>-10.49253190285714</v>
       </c>
       <c r="P92">
-        <v>-58.07466074285714</v>
+        <v>-59.45768078285712</v>
       </c>
       <c r="Q92">
-        <v>-5.474660742857147</v>
+        <v>-6.85768078285713</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.7306237815625252</v>
+        <v>0.8067153128472502</v>
       </c>
       <c r="T92">
-        <v>8.925549609523841</v>
+        <v>9.91727734391538</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.08001467915237494</v>
+        <v>0.07913539696388731</v>
       </c>
       <c r="W92">
-        <v>0.1847330524262031</v>
+        <v>0.1849096122896514</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5334311943491663</v>
+        <v>0.5275693130925823</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2408721253398353</v>
+        <v>0.2424221253398353</v>
       </c>
       <c r="C93">
-        <v>-412.1688097538242</v>
+        <v>-422.7337478192628</v>
       </c>
       <c r="D93">
-        <v>312.3041902461758</v>
+        <v>309.8422521807373</v>
       </c>
       <c r="E93">
-        <v>481.1729999999999</v>
+        <v>489.276</v>
       </c>
       <c r="F93">
-        <v>737.3729999999999</v>
+        <v>745.476</v>
       </c>
       <c r="G93">
         <v>12.9</v>
@@ -8901,37 +8901,37 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M93">
-        <v>148.0644984</v>
+        <v>149.6915808</v>
       </c>
       <c r="N93">
-        <v>-69.95021268571426</v>
+        <v>-71.57729508571427</v>
       </c>
       <c r="O93">
-        <v>-10.49253190285714</v>
+        <v>-10.73659426285714</v>
       </c>
       <c r="P93">
-        <v>-59.45768078285712</v>
+        <v>-60.84070082285713</v>
       </c>
       <c r="Q93">
-        <v>-6.85768078285713</v>
+        <v>-8.240700822857136</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.8067153128472502</v>
+        <v>0.9018297269531567</v>
       </c>
       <c r="T93">
-        <v>9.91727734391538</v>
+        <v>11.15693701190481</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.07913539696388731</v>
+        <v>0.0782752296055842</v>
       </c>
       <c r="W93">
-        <v>0.1849096122896514</v>
+        <v>0.1850823338951987</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5275693130925823</v>
+        <v>0.521834864037228</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2424221253398353</v>
+        <v>0.2439721253398353</v>
       </c>
       <c r="C94">
-        <v>-422.7337478192628</v>
+        <v>-433.2601738689989</v>
       </c>
       <c r="D94">
-        <v>309.8422521807373</v>
+        <v>307.418826131001</v>
       </c>
       <c r="E94">
-        <v>489.276</v>
+        <v>497.379</v>
       </c>
       <c r="F94">
-        <v>745.476</v>
+        <v>753.579</v>
       </c>
       <c r="G94">
         <v>12.9</v>
@@ -8983,37 +8983,37 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M94">
-        <v>149.6915808</v>
+        <v>151.3186632</v>
       </c>
       <c r="N94">
-        <v>-71.57729508571427</v>
+        <v>-73.20437748571428</v>
       </c>
       <c r="O94">
-        <v>-10.73659426285714</v>
+        <v>-10.98065662285714</v>
       </c>
       <c r="P94">
-        <v>-60.84070082285713</v>
+        <v>-62.22372086285714</v>
       </c>
       <c r="Q94">
-        <v>-8.240700822857136</v>
+        <v>-9.623720862857141</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.9018297269531567</v>
+        <v>1.024119687946465</v>
       </c>
       <c r="T94">
-        <v>11.15693701190481</v>
+        <v>12.75078515646264</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.0782752296055842</v>
+        <v>0.07743356047004028</v>
       </c>
       <c r="W94">
-        <v>0.1850823338951987</v>
+        <v>0.1852513410576159</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.521834864037228</v>
+        <v>0.5162237364669352</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2439721253398353</v>
+        <v>0.2455221253398353</v>
       </c>
       <c r="C95">
-        <v>-433.2601738689989</v>
+        <v>-443.7489845531797</v>
       </c>
       <c r="D95">
-        <v>307.418826131001</v>
+        <v>305.0330154468203</v>
       </c>
       <c r="E95">
-        <v>497.379</v>
+        <v>505.482</v>
       </c>
       <c r="F95">
-        <v>753.579</v>
+        <v>761.682</v>
       </c>
       <c r="G95">
         <v>12.9</v>
@@ -9065,37 +9065,37 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M95">
-        <v>151.3186632</v>
+        <v>152.9457456</v>
       </c>
       <c r="N95">
-        <v>-73.20437748571428</v>
+        <v>-74.83145988571428</v>
       </c>
       <c r="O95">
-        <v>-10.98065662285714</v>
+        <v>-11.22471898285714</v>
       </c>
       <c r="P95">
-        <v>-62.22372086285714</v>
+        <v>-63.60674090285714</v>
       </c>
       <c r="Q95">
-        <v>-9.623720862857141</v>
+        <v>-11.00674090285715</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.024119687946465</v>
+        <v>1.187172969270876</v>
       </c>
       <c r="T95">
-        <v>12.75078515646264</v>
+        <v>14.87591601587308</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.07743356047004028</v>
+        <v>0.0766097991884441</v>
       </c>
       <c r="W95">
-        <v>0.1852513410576159</v>
+        <v>0.1854167523229604</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.5162237364669352</v>
+        <v>0.5107319945896274</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2455221253398353</v>
+        <v>0.2470721253398353</v>
       </c>
       <c r="C96">
-        <v>-443.7489845531797</v>
+        <v>-454.2010489014806</v>
       </c>
       <c r="D96">
-        <v>305.0330154468203</v>
+        <v>302.6839510985194</v>
       </c>
       <c r="E96">
-        <v>505.482</v>
+        <v>513.585</v>
       </c>
       <c r="F96">
-        <v>761.682</v>
+        <v>769.785</v>
       </c>
       <c r="G96">
         <v>12.9</v>
@@ -9147,37 +9147,37 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M96">
-        <v>152.9457456</v>
+        <v>154.572828</v>
       </c>
       <c r="N96">
-        <v>-74.83145988571428</v>
+        <v>-76.45854228571426</v>
       </c>
       <c r="O96">
-        <v>-11.22471898285714</v>
+        <v>-11.46878134285714</v>
       </c>
       <c r="P96">
-        <v>-63.60674090285714</v>
+        <v>-64.98976094285712</v>
       </c>
       <c r="Q96">
-        <v>-11.00674090285715</v>
+        <v>-12.38976094285712</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.187172969270876</v>
+        <v>1.415447563125052</v>
       </c>
       <c r="T96">
-        <v>14.87591601587308</v>
+        <v>17.8510992190477</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.0766097991884441</v>
+        <v>0.07580338024961839</v>
       </c>
       <c r="W96">
-        <v>0.1854167523229604</v>
+        <v>0.1855786812458766</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.5107319945896274</v>
+        <v>0.5053558683307893</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2470721253398353</v>
+        <v>0.2486221253398353</v>
       </c>
       <c r="C97">
-        <v>-454.2010489014806</v>
+        <v>-464.6172093785077</v>
       </c>
       <c r="D97">
-        <v>302.6839510985194</v>
+        <v>300.3707906214924</v>
       </c>
       <c r="E97">
-        <v>513.585</v>
+        <v>521.6880000000001</v>
       </c>
       <c r="F97">
-        <v>769.785</v>
+        <v>777.888</v>
       </c>
       <c r="G97">
         <v>12.9</v>
@@ -9229,37 +9229,37 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M97">
-        <v>154.572828</v>
+        <v>156.1999104</v>
       </c>
       <c r="N97">
-        <v>-76.45854228571426</v>
+        <v>-78.08562468571429</v>
       </c>
       <c r="O97">
-        <v>-11.46878134285714</v>
+        <v>-11.71284370285714</v>
       </c>
       <c r="P97">
-        <v>-64.98976094285712</v>
+        <v>-66.37278098285715</v>
       </c>
       <c r="Q97">
-        <v>-12.38976094285712</v>
+        <v>-13.77278098285716</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.415447563125052</v>
+        <v>1.757859453906316</v>
       </c>
       <c r="T97">
-        <v>17.8510992190477</v>
+        <v>22.31387402380964</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.07580338024961839</v>
+        <v>0.07501376170535151</v>
       </c>
       <c r="W97">
-        <v>0.1855786812458766</v>
+        <v>0.1857372366495654</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.5053558683307893</v>
+        <v>0.5000917447023434</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2486221253398353</v>
+        <v>0.2849109372533374</v>
       </c>
       <c r="C98">
-        <v>-464.6172093785074</v>
+        <v>-518.3061589397549</v>
       </c>
       <c r="D98">
-        <v>300.3707906214925</v>
+        <v>254.784841060245</v>
       </c>
       <c r="E98">
-        <v>521.6879999999999</v>
+        <v>529.7909999999999</v>
       </c>
       <c r="F98">
-        <v>777.8879999999999</v>
+        <v>785.991</v>
       </c>
       <c r="G98">
         <v>12.9</v>
@@ -9311,45 +9311,45 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M98">
-        <v>156.1999104</v>
+        <v>185.3366778</v>
       </c>
       <c r="N98">
-        <v>-78.08562468571427</v>
+        <v>-107.2223920857143</v>
       </c>
       <c r="O98">
-        <v>-11.71284370285714</v>
+        <v>-16.08335881285714</v>
       </c>
       <c r="P98">
-        <v>-66.37278098285712</v>
+        <v>-91.13903327285715</v>
       </c>
       <c r="Q98">
-        <v>-13.77278098285713</v>
+        <v>-38.53903327285715</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.757859453906311</v>
+        <v>2.354839668991816</v>
       </c>
       <c r="T98">
-        <v>22.31387402380958</v>
+        <v>30.09452748402152</v>
       </c>
       <c r="U98">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.07501376170535153</v>
+        <v>0.06322085297000429</v>
       </c>
       <c r="W98">
-        <v>0.1857372366495654</v>
+        <v>0.220892522869673</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y98">
-        <v>0.5000917447023435</v>
+        <v>0.421472353133362</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2849109372533374</v>
+        <v>0.2868109372533374</v>
       </c>
       <c r="C99">
-        <v>-518.3061589397549</v>
+        <v>-528.4177449546942</v>
       </c>
       <c r="D99">
-        <v>254.784841060245</v>
+        <v>252.7762550453057</v>
       </c>
       <c r="E99">
-        <v>529.7909999999999</v>
+        <v>537.894</v>
       </c>
       <c r="F99">
-        <v>785.991</v>
+        <v>794.0939999999999</v>
       </c>
       <c r="G99">
         <v>12.9</v>
@@ -9393,37 +9393,37 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M99">
-        <v>185.3366778</v>
+        <v>187.2473652</v>
       </c>
       <c r="N99">
-        <v>-107.2223920857143</v>
+        <v>-109.1330794857143</v>
       </c>
       <c r="O99">
-        <v>-16.08335881285714</v>
+        <v>-16.36996192285714</v>
       </c>
       <c r="P99">
-        <v>-91.13903327285715</v>
+        <v>-92.76311756285712</v>
       </c>
       <c r="Q99">
-        <v>-38.53903327285715</v>
+        <v>-40.16311756285712</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.354839668991816</v>
+        <v>3.509359503487724</v>
       </c>
       <c r="T99">
-        <v>30.09452748402152</v>
+        <v>45.14179122603228</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.06322085297000429</v>
+        <v>0.06257574222541241</v>
       </c>
       <c r="W99">
-        <v>0.220892522869673</v>
+        <v>0.2210446399832478</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.421472353133362</v>
+        <v>0.4171716148360828</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2868109372533374</v>
+        <v>0.2887109372533374</v>
       </c>
       <c r="C100">
-        <v>-528.4177449546942</v>
+        <v>-538.4979094661678</v>
       </c>
       <c r="D100">
-        <v>252.7762550453057</v>
+        <v>250.7990905338322</v>
       </c>
       <c r="E100">
-        <v>537.894</v>
+        <v>545.9970000000001</v>
       </c>
       <c r="F100">
-        <v>794.0939999999999</v>
+        <v>802.197</v>
       </c>
       <c r="G100">
         <v>12.9</v>
@@ -9475,37 +9475,37 @@
         <v>78.11428571428573</v>
       </c>
       <c r="M100">
-        <v>187.2473652</v>
+        <v>189.1580526</v>
       </c>
       <c r="N100">
-        <v>-109.1330794857143</v>
+        <v>-111.0437668857143</v>
       </c>
       <c r="O100">
-        <v>-16.36996192285714</v>
+        <v>-16.65656503285714</v>
       </c>
       <c r="P100">
-        <v>-92.76311756285712</v>
+        <v>-94.38720185285715</v>
       </c>
       <c r="Q100">
-        <v>-40.16311756285712</v>
+        <v>-41.78720185285715</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.509359503487724</v>
+        <v>6.972919006975448</v>
       </c>
       <c r="T100">
-        <v>45.14179122603228</v>
+        <v>90.28358245206455</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.06257574222541241</v>
+        <v>0.06194366402111531</v>
       </c>
       <c r="W100">
-        <v>0.2210446399832478</v>
+        <v>0.221193684023821</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.4171716148360828</v>
+        <v>0.4129577601407688</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2887109372533374</v>
-      </c>
-      <c r="C101">
-        <v>-538.4979094661678</v>
-      </c>
-      <c r="D101">
-        <v>250.7990905338322</v>
-      </c>
-      <c r="E101">
-        <v>545.9970000000001</v>
-      </c>
-      <c r="F101">
-        <v>802.197</v>
-      </c>
-      <c r="G101">
-        <v>12.9</v>
-      </c>
-      <c r="H101">
-        <v>554.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>130.7142857142857</v>
-      </c>
-      <c r="K101">
-        <v>52.59999999999999</v>
-      </c>
-      <c r="L101">
-        <v>78.11428571428573</v>
-      </c>
-      <c r="M101">
-        <v>189.1580526</v>
-      </c>
-      <c r="N101">
-        <v>-111.0437668857143</v>
-      </c>
-      <c r="O101">
-        <v>-16.65656503285714</v>
-      </c>
-      <c r="P101">
-        <v>-94.38720185285715</v>
-      </c>
-      <c r="Q101">
-        <v>-41.78720185285715</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>6.972919006975448</v>
-      </c>
-      <c r="T101">
-        <v>90.28358245206455</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.06194366402111531</v>
-      </c>
-      <c r="W101">
-        <v>0.221193684023821</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.4129577601407688</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
